--- a/public/Academic Projects.xlsx
+++ b/public/Academic Projects.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y3"/>
+  <dimension ref="A1:Y32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,3390 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46249.48421563658</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>gracemariareji.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Main Project</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aerial holographic teaching system using AR</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>This paper proposes an Augmented Reality (AR)-based Mobile-Assisted Language Learning (MALL) framework that addresses the conversational and environmental limitations of conventional digital language learning systems. Traditional MALL applications primarily rely on screen-based exercises, enabling vocabulary acquisition but providing limited support for real-world conversational skills. The proposed framework, developed using Unity and Google ARCore, integrates environmental understanding with cloud-based Large Language Models (LLMs) and Speech-to-Text (STT) models to analyze the learner’s surroundings, grammar, and pronunciation in real time. Unlike existing approaches, the system anchors AI-generated feedback directly onto detected real-world objects, allowing learners to associate vocabulary and grammar with physical contexts, thereby improving contextual understanding and long-term retention.
+The framework employs a closed-loop architecture comprising spatial perception, prompt generation, linguistic reasoning, and immersive AR visualization. Mathematical models for vocabulary accuracy, pronunciation scoring, and semantic consistency provide objective and reproducible performance evaluation. A two-week study involving 24 participants compared the proposed AR-based learning approach with a conventional screen-based method. Experimental results demonstrated a 34.7% improvement in contextual vocabulary acquisition, 72.4% pronunciation accuracy, and an average learner motivation score of 4.3/5, outperforming traditional learning techniques. These findings indicate that integrating AR with AI-driven language understanding effectively bridges the gap between declarative vocabulary knowledge and practical communication skills by embedding language learning within the learner’s physical environment.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AI Nd AR</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1zHzdEKslpTQHleSwvSotFOO-m_ThgQTS</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=179dnjkcVUbgfpTdHmE5Fcd96jcZ8h-Oo</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Dr Sajitha A S</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grace Maria Reji </t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC23AD028 </t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://github.com/Gracereji</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUSTIN JEESON </t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>JEC23AD020</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SHREYAS S</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>JEC23AD053</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>IMG-20260806-WA0041 - 12317028 GRACE MARIA REJI.jpg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Screenshot_20260815_113530_WhatsApp - 12317028 GRACE MARIA REJI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46249.60343123843</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>abiealjoby.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Fraud Detection with Explainable AI (SHAP)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fraud Detection with Explainable AI (SHAP) is a machine learning-based system designed to detect fraudulent financial transactions and provide understandable explanations for the predictions. The project uses transaction-related features such as transaction type, transaction amount, sender and receiver balances, and transaction step to classify transactions as fraudulent or non-fraudulent.
+The dataset is first analyzed and preprocessed using exploratory data analysis, missing-value checking, categorical encoding, and outlier handling. A Random Forest Classifier is trained to identify patterns associated with fraudulent transactions. The model uses balanced class weights to improve its ability to detect fraud in an imbalanced dataset.
+A major focus of the project is Explainable Artificial Intelligence (XAI) using SHAP (SHapley Additive exPlanations). SHAP is used to understand which features influence the model's predictions. A SHAP beeswarm plot provides a global explanation of feature importance, while a SHAP waterfall plot explains the contribution of individual features for a particular transaction.
+The system also provides single-transaction prediction functionality, where a user can enter transaction details and obtain the predicted class and fraud probability along with a SHAP-based explanation. Model performance is evaluated using classification metrics, a confusion matrix, and ROC-AUC.
+The project demonstrates how machine learning and explainable AI can be combined to build a more transparent fraud detection system, helping users understand not only whether a transaction is fraudulent but also why the model considers it suspicious.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Python, Machine Learning, Random Forest, SHAP, Explainable AI, Pandas, Scikit-learn, Data Visualization</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1QPyoLsLMp6jxZvCDVJC7vqfoVeQ1xuT-</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1gj9qsQIsu_7RPIExrawXVjujp5iuLPLv</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Divya konikkara</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABIEAL JOBY </t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC24AD004 </t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://github.com/abieal/Fraud-Detection-With-Explainable-AI-shap-</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>FAHAD ABOOBACKER N S</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>JEC24AD039</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>AISWARYA KALLAYIL RAJESH</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>JEC24AD007</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>AYSHA ABDUL HAQUE P P</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>JEC24AD028</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>fraud_detection_explainable_ai_cover_under_1mb - 12417004 ABIEAL JOBY.jpg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>fraud_detection_working_demo_under_1mb - 12417004 ABIEAL JOBY.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46249.64578863426</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>gracemariareji.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mini Project</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI for Real-time Language Learning with Augmented Reality </t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This paper proposes an augmented reality (AR)
+mobile language learning framework with an understanding of
+the environment that addresses the conversational and envi-
+ronmental shortcomings of traditional digital educational ap-
+proaches. Traditional MALL applications primarily limit lan-
+guage learning to exercises constrained on the screen, resulting
+in learners gaining solid declarative vocabulary knowledge yet
+having difficulty applying it in actual conversation. The proposed
+application utilizes Unity and Google ARCore to provide more
+advanced features than just surface tracking by integrating an
+AI pipeline that combines sensor information with cloud-based
+large language models and speech-to-text models for analyzing
+the environment, grammar, and pronunciation in real time. The
+fact that generation of feedback is anchored directly onto detected
+surfaces of the environment provides an opportunity to help
+learners link new vocabulary and grammar with the objects in
+the environment, thus enhancing memorization through spatial
+and contextual references rather than repetition.
+The architecture utilizes a closed-loop execution stack in-
+corporating spatial awareness, prompt composition, linguistic
+reasoning, and immersive visualization, and additionally includes
+mathematical models for lexicon accuracy, phonetic scoring,
+and semantic drift recognition to guarantee objective, replicable
+performance assessment. The results of the experiment, which
+was performed on 24 subjects for two weeks in total and included
+an experimental group learning through AR technology and
+a control group learning using a traditional screen interface,
+showed a 34.7% increase in contextual vocabulary acquisition,
+72.4% pronunciation accuracy, and a 4.3/5 learner motivation
+score relative to conventional baseline learning approaches .
+It is shown that this research helps overcome the problem of
+transitioning from declarative lexicon knowledge to communica-
+tion abilities by anchoring linguistic scaffolds into the physical
+surroundings of the learner.
+</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Augmented Reality, Large Language Models, Mobile-Assisted Language Learning, Environmental Awareness, Speech-to-Text, Pronunciation Scoring, ARCore, Unity, Spatial Anchoring, Contextual Vocabulary </t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=13HMHkpjqVAL0kz-XMMBdn_oCE_et-KwD</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=183tt85WS9JVumX32_It6LrlvQsuAQtXK</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Dr.sajitha A S</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grace Maria Reji </t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC23AD028 </t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://github.com/Gracereji</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Austin Jeeson </t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>JEC23AD020</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SHREYAS S</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>JEC23AD053</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>AI_Language_Learning_AR_Cover_Under_1MB-8 - 12317028 GRACE MARIA REJI.jpg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>IMG-20260316-WA0029 - 12317028 GRACE MARIA REJI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46249.82735542824</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>aiswaryakallayilrajesh.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MEMORY SYSTEM-CACHE AND VIRTUAL  MEMORY</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>The project titled “Memory system cache and virtual memory” ,The rapid advancement 
+of computing systems has increased the demand for high-speed and efficient memory 
+management techniques. One of the major challenges in computer architecture is the 
+significant speed gap between the processor and main memory, which can lead to performance 
+bottlenecks. To address this issue, cache memory is used as a high-speed storage layer that 
+stores frequently accessed data, thereby reducing memory access time. In addition, virtual 
+memory enables systems to execute programs larger than the available physical memory by 
+using techniques such as paging and page replacement algorithms.
+This project focuses on the study and simulation of cache memory and virtual memory 
+to analyze their impact on system performance. Cache memory behavior is simulated using 
+the Ripes simulator with a direct-mapped cache configuration. A RISC-V assembly program 
+is executed to observe cache hits and misses, highlighting concepts such as temporal locality 
+and conflict misses. The performance is evaluated by measuring cache hit rates and miss rates 
+under different conditions.
+Virtual memory is analyzed using the FIFO (First-In-First-Out) page replacement 
+algorithm. A reference string is used to simulate page accesses, and the number of page faults 
+and page hits are recorded. The study also demonstrates how limited memory frames can lead 
+to frequent page faults and the phenomenon of thrashing, which negatively affects system 
+performance.
+The results show that cache memory significantly improves system speed after initial 
+compulsory misses, while virtual memory enhances memory utilization but may introduce 
+overhead due to page faults. The project highlights the importance of efficient memory 
+management techniques and provides insights into optimizing system performance through 
+proper cache configuration and page replacement strategies.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>RISC-V, Ripes Simulator, Assembly Language, Cache Memory, Virtual Memory, FIFO Page Replacement</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1h1tZwJAfcPp7WLR6KMllE1GhBGy_-j58</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=15YbO40XHXknz2admbCyjgcA2-IkRYcmo</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Dr. Sandeep C S</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aiswarya Kallayil Rajesh </t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>JEC24AD007</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>aiswaryakallayilrajesh.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alan Alexander </t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>JEC24AD011</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Anirudh P S</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>JEC24AD016</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Anjana P A</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>JEC24AD017</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>memory_system_cover_under_1MB - 12417007 AISWARYA KALLAYIL RAJESH.jpg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>project_working_demo_under_1MB - 12417007 AISWARYA KALLAYIL RAJESH.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46249.8493425</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>seannaks.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Public complaint resolution tracking system </t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>The Public Complaint &amp; Resolution Tracking System is a web-based application developed to simplify and improve the process of registering, managing, and resolving public complaints. The system allows users to submit complaints related to public services and track their status online. Administrators can view complaints, assign them to the appropriate authorities, update their progress, and record the resolution. The system provides transparency, reduces manual paperwork, and helps ensure that complaints are handled efficiently and within a reasonable time. Overall, the project aims to create a more organized, accountable, and user-friendly complaint management process.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Web Development , Database Management,React.js, Node.js, Express.js, MySQL, HTML, CSS, JavaScript</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1SSi_kaadRJAqsZXB43qYbo9GJkFe3_Ls</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1dmWmVRygzAdAUBkzk9LQScKNVewlZIUC</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Seanna K S</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>JEC24AD078</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>seannasubash@gmail.com</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Nithali Chandran</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>JEC24AD067</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sona C P</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>JEC24AD082</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Sreelakshmi P</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>JEC24AD086</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>IMAGE (3) - 12417077 SEANNA K S.png</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>IMAGE (2) - 12417077 SEANNA K S.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46249.85844240741</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>hibarebink.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mini Project</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive EV Charging Stop Optimization </t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>The rapid growth of Electric Vehicles (EVs) has
+increased the need for the efficient management of the charging
+infrastructure. One of the biggest challenges for EV users is
+the uncertainty around availability of charging stations and the
+waiting time, often referred to as wait-time anxiety. Traditional
+navigation systems can guide users to the nearest charging
+stations, but provide no information about congestion or waiting
+time. The project proposes a machine-learning based framework
+called Predictive EV Charging Stop Optimization.The goal is to
+decrease overall travel time delays through intelligent selection
+of the right charging station. The system uses data from past
+charging sessions and time series prediction algorithms such
+as LSTM to predict the occupancy level and waiting time
+at the stations. The multi-factor optimization engine predicts
+reachable charging stations based on the total time lost, which
+includes detour driving time, the predicted waiting time, and the
+charging time. The framework is implemented as a real-time web
+platform with backend APIs, battery-aware reachability filtering,
+and interactive dashboard visualization to help trip planning
+decisions.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Machine learning,  Python,  FastAPI, React, ARIMA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1bLjXrROEkY9Yv7wbzo4MiLOziE20uYnZ</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1TXF425AOMrI61wzI5EhvKI9hzWqgQxQU</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Ms. LINTA AT</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Hiba rebin k</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC23AD029 </t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hibarebink.ad23@jecc.ac.in </t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Irine Vincent</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>JEC23AD030</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Muhammed Shiyas M</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC23AD041 </t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Pavan R Kumar</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>JEC23AD046</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>IMG-20260815-WA0023 - 12317029 HIBA REBIN K.jpg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>IMG-20260815-WA0069 - 12317029 HIBA REBIN K.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46249.86108936342</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>abhinavsk.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Driver Drowsiness Detection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Driver Drowsiness Detection is a deep learning and computer vision-based system developed to identify early signs of driver fatigue by monitoring the driver's eye state. The project uses a Convolutional Neural Network (CNN) to classify eye images into two categories: open eyes and closed eyes. The dataset consists of thousands of labeled eye images collected from publicly available sources. To improve model performance and generalization, the images were preprocessed through resizing, normalization, and data augmentation techniques such as rotation, shifting, zooming, horizontal flipping, and brightness adjustment. The dataset was divided into training, validation, and testing sets for effective model development and evaluation. The model was implemented using Python and TensorFlow in Google Colab and evaluated using accuracy, confusion matrix, precision, recall, F1-score, and ROC curve. The final model achieved 95.0% training accuracy, 93.8% validation accuracy, 95.2% precision, 95.0% recall, 94.8% F1-score, and an ROC value of 0.97. The project demonstrates how Artificial Intelligence and Computer Vision can be applied to improve road safety by detecting potential driver drowsiness. Future enhancements include real-time video processing, alarm or vibration alerts, and deployment on embedded platforms for practical vehicle applications.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Data Science, AI, Computer Vision, Deep Learning, Python, TensorFlow, CNN, OpenCV</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=18Nkf4cQXLvkm6XMQazNpmHhKDTHWM3Ek</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1e1rF0MCJdyWYy4o8arc4J-nunWkvDImJ</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Ms. Divya Konikkara</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Abhinav sk</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>JEC24AD003</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>skabhinav5656@gmail.com</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Aswathy S</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>JEC24AD026</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Faris Jafer Sadik</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>JEC24AD040</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Hannah Margret M S</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>JEC24AD044</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>driver detection image - 12417003 ABHINAV S K.jpeg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Driver_Drowsiness_Working_Demo - 12417003 ABHINAV S K.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46249.87296578704</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ayshashafeek.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Water potability prediction using machine learning</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Water quality is a critical factor in ensuring public health and sustainable living. The increasing contamination of natural water sources due to industrialization and urbanization has made it essential to assess the potability of water efficiently. This project focuses on predicting the potability of water using machine learning techniques, aiming to automate and improve the reliability of water quality assessment. The main objective is to build a predictive model that can classify water samples as potable or non-potable based on various physicochemical properties such as pH, hardness, solids, chloramines, sulfate, conductivity, organic carbon, trihalomethanes, and turbidity. The study uses the publicly available Water Potability Dataset obtained from Kaggle, which contains 2180 samples with multiple numerical features describing water characteristics. Data preprocessing steps such as handling missing values, normalization, and feature selection were applied to ensure better model accuracy. Several supervised learning algorithms, including Logistic Regression, Random Forest, and k-Nearest Neighbors, were trained and tested to determine the best-performing model. The models were evaluated using performance metrics such as accuracy, precision, recall, F1-score, and the area under the ROC curve to measure their classification effectiveness. Among the tested models, the Random Forest classifier achieved the highest performance, demonstrating its robustness in handling complex feature relationships. The project highlights the potential of machine learning in supporting environmental monitoring and decision-making for safe drinking water. The findings contribute to Sustainable Development Goals (SDG 3 and SDG 6) by promoting good health and clean water for all. In the future, the model can be improved by incorporating real-time water quality data and deploying it as an intelligent monitoring system to assist water management authorities and public health organizations.
+</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Machine learning, Data Science</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1dxT9CNbpItNv493Zd3VTxEv9SfbpPna6</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1-6Ew-weum0VvXlNdqjpTdbCCgFIZxT4F</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Ms. Divya Konikkara</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Aysha shafeek</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>JEC24AD030</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ayshashafeek205@gmail.com</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Asna A</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>JEC24AD025</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anirudh P S </t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>JEC24AD016</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>AI image - 12417030 AYSHA SHAFEEK.jpg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>project demo - 12417030 AYSHA SHAFEEK.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46249.88104824074</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>abhinavsk.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pipeline Hazards and Performance Analysis Using RIPES</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pipeline Hazards and Performance Analysis Using RIPES is a simulation-based micro project that studies the behaviour of pipelined RISC-V processors and analyses how pipeline hazards affect instruction execution and processor performance. The project focuses mainly on data hazards and control hazards, which can cause pipeline stalls, incorrect instruction fetching, and increased execution time. RISC-V assembly programs were designed to intentionally create instruction dependencies and branch-related control hazards. These programs were implemented and executed using the RIPES simulator, which provides a graphical representation of the processor, pipeline stages, registers, instruction flow, and execution information. The project uses the 5-stage pipeline consisting of Instruction Fetch (IF), Instruction Decode (ID), Execute (EX), Memory Access (MEM), and Write Back (WB). The programs were executed step-by-step to observe instruction movement and identify the effects of hazards. Performance was analysed using execution metrics such as cycles, CPI, and IPC. The project provides practical understanding of pipelined processor operation and demonstrates how hazards reduce pipeline efficiency. It also highlights the importance of techniques such as forwarding, stalling, and branch prediction in reducing the performance impact of hazards.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>RISC-V, RIPES, Assembly Language, Computer Architecture, Pipelining, Simulation</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1khOha5R8E8Z1OTSDX0kuJJPRvhzzMRJe</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=18UHEUZAlLeQmWnIhkhwydmI0GqlPkByN</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Dr. Sandeep C S</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Abhinav sk</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>JEC24AD003</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>skabhinav5656@gmail.com</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Adhisree P A</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>JEC24AD006</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gowri Sooraj</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>JEC24AD042</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>coa image - 12417003 ABHINAV S K.jpeg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>COA_RIPES_Figure_Working_Demo - 12417003 ABHINAV S K.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46249.88267362268</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>keerthanab.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>An AI-Assisted Hybrid Database System  for Monitoring Road Environmental Compliance</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rapid road infrastructure development frequently introduces environmental hazards such as excessive noise, particulate emissions, water contamination, vibration, and ecological disruption. Conventional compliance monitoring relies on manual inspection and periodic reporting, resulting in delayed violation detection, inconsistent recordkeeping, and weak regulatory enforcement. This paper presents an expanded and AI-integrated design of the RoadGuard Road Environmental Compliance Monitoring System, a hybrid database architecture that combines the structural rigor of MySQL with the schema flexibility of MongoDB to manage, respectively, regulatory/administrative data and high-frequency environmental sensor data. A Python-based middleware engine continuously retrieves legal thresholds and live sensor readings, performs automated compliance verification, classifies violations by severity, and triggers alerts that are logged and visualized on an interactive dashboard. The paper details the system architecture, module-level design, automated compliance detection algorithm, and a prompt-engineering framework through which large language models can assist in explaining violations and drafting inspector-facing summaries. A comparative performance evaluation against manual inspection workflows indicates substantial gains in detection accuracy, alert latency, scalability, and storage efficiency. The proposed framework strengthens transparency, accountability, and data-driven governance in road construction projects and establishes a foundation for future IoT, GIS, and predictive-analytics extensions.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1iU2m-fc6dcqSHSdH1xvajexTLJwPepCW</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1z25oqcFg8SebQbLbeDbqT7R7LevAUXbK</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Jithin KC</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Keerthana B </t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>JEC24AD053</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>keerthanabijulesh@gmail.com,(https://roadguard-4ksm1zurw-nashwashirins-projects.vercel.app)</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nashwa Shirin K </t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>JEC24AD063</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neha Nafeesa MK </t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>JEC24AD064</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Screenshot_20260815-205945 - 12417054 KEERTHANA B.png</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Screenshot_20260815-210147 - 12417054 KEERTHANA B.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46249.89212006945</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sanafathimapb.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Library Management System </t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>The rapid digital transformation of educational institutions and knowledge centers has
+necessitated the development of robust, scalable, and adaptable database architectures for
+modern library systems capable of efficiently managing both structured transactional records
+and diverse, evolving resource metadata. Traditional monolithic Relational Database
+Management Systems (RDBMS), while highly effective in enforcing ACID properties and
+ensuring transactional integrity, often encounter structural limitations when handling flexible,
+category-specific attributes associated with varied library materials such as technical books,
+children’s literature, reference works, and digital resources, frequently resulting in rigid
+schemas, sparse tables, and reduced scalability as collections expand. In response to these
+challenges, this micro-project presents the design and implementation of an advanced Library
+Management System built on a hybrid architecture inspired by the concept of Polyglot
+Persistence, integrating a relational database (PostgreSQL) to manage core operational entities
+including Books, Members, Transactions, Authors, and Staff, thereby ensuring consistency,
+reliability, and enforcement of complex business rules, while simultaneously employing a
+NoSQL document database (MongoDB) to accommodate flexible and semi-structured data
+such as detailed book descriptions, category-specific attributes, and user-generated reviews.
+Furthermore, the system incorporates advanced database-level logic through the
+implementation of PL/pgSQL triggers for real-time stock validation and automatic inventory
+updates during borrowing and return operations, along with stored procedures utilizing
+appropriate locking mechanisms to prevent concurrency issues such as duplicate issuance,
+race conditions, and inconsistent stock states during simultaneous transactions. The resulting
+platform demonstrates a scalable, highly consistent, and future-ready backend architecture
+that effectively balances transactional safety with schema flexibility, providing a resilient and
+efficient framework capable of supporting expanding library collections, increasing user
+activity, and evolving academic requirements.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PostgreSQL, MongoDB, PL/pgSQL, SQL, Database Management System, NoSQL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=114xfwCx-CIzNZVZG2Tg5HT5sxZVOeybC</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1YhuEqjpObmaOG3-5TB8EHBXMleNxGFJB</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Jithin K.C</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sana Fathima P.B </t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC24AD076 </t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Sanafathima97388@gmail.com</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Joel V G</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>JEC24AD048</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Malavika P Santhosh</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>JEC24AD059</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samuel Shaju T </t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>JEC24AD075</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>IMG-20260815-WA0045 - 12417075 SANA FATHIMA P B.jpg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>IMG-20260815-WA0051 - 12417075 SANA FATHIMA P B.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46249.8932746875</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>sreyakrishnan.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Road Accident Risk Prediction using Machine Learning Techniques</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Road Accident Risk Prediction using Machine Learning Techniques is a machine learning-based project developed to predict road accident risk based on various factors such as time, weather conditions, road conditions, driver details, vehicle information, and other accident-related features. The main objective is to identify accident-prone areas and high-risk time periods, enabling preventive measures to improve road safety.
+The project uses the RTA Dataset.csv, a secondary dataset obtained from Kaggle, containing 12,316 records and 32 features. Since the raw dataset contains missing values, categorical data, and inconsistent data types, preprocessing techniques such as missing-value treatment using mode imputation, duplicate checking, outlier detection using the IQR method, and Label Encoding were applied. 
+PBADT304_MicroProjectReport ds final.pdf
+To address class imbalance in accident severity, SMOTE (Synthetic Minority Over-sampling Technique) was applied. Feature engineering was performed by extracting the hour from the Time column and creating features such as Casualty Rate and Is Peak Hour. 
+PBADT304_MicroProjectReport ds final.pdf
+PBADT304_MicroProjectReport ds final.pdf
+Two classification models, Random Forest and XGBoost, were trained and compared. Random Forest achieved 97% accuracy, while XGBoost achieved 100% accuracy on the reported test data. Considering stability, generalization, and the possibility of overfitting, Random Forest was selected as the final model. 
+PBADT304_MicroProjectReport ds final.pdf
+The proposed system can assist traffic authorities and urban planners in identifying high-risk conditions and accident-prone areas, supporting early preventive actions and safer transportation systems. The project also contributes to SDG 3 (Good Health and Well-being) and SDG 11 (Sustainable Cities and Communities).</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Machine Learning, Python, Data Science, Random Forest</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1RWVezID5BXqkmdNLnEpuANgDZ3frfa_l</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1eog5_0gHzo3BjtWImCfomKdEACP6atoC</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Dr.Parvathy Jyothi</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sreya Krishnan </t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>JEC24AD087</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>sreyakrishnan117@gmail.com</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Pavandas S</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>JEC24AD070</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Paul Dix</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>JEC24AD069</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Nanditha Madhavan C M</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>LJEC24AD095</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Road-accident - 12417086 SREYA KRISHNAN.jpeg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Demo - 12417086 SREYA KRISHNAN.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46249.89956996528</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>sreyakrishnan.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simple RISC-V Based Calculator </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>The “Simple RISC-V Based Calculator” is a processor-level calculator designed and implemented using the RISC-V Instruction Set Architecture (ISA) and RISC-V assembly language. The project demonstrates how basic arithmetic operations can be performed directly at the processor level using registers, the Arithmetic Logic Unit (ALU), and control flow instructions.
+The calculator performs four fundamental arithmetic operations: addition, subtraction, multiplication, and division. Input operands are stored in general-purpose registers, and the corresponding RISC-V instructions are used to perform the required computation. The calculated results are stored in designated registers and verified through the Ripes microarchitectural simulator.
+A key feature of the project is its risk-free execution mechanism for handling exceptional conditions, particularly division by zero. Before performing a division operation, the program checks whether the divisor is zero using a conditional branch instruction. If a zero divisor is detected, the program redirects execution to an error-handling routine instead of performing an invalid computation. This ensures reliable and safe program execution.
+The project is implemented and tested using the Ripes simulator, which provides a visual representation of the processor datapath, registers, ALU, instruction memory, and instruction execution flow. It also allows the execution of RISC-V instructions to be observed through different processor stages, helping in the verification of register values and computational results.
+The main objective of this project is to provide a practical understanding of RISC-V architecture, assembly-level programming, register-based computation, ALU operations, instruction sequencing, branching, and processor-level execution. The project successfully bridges the gap between theoretical concepts of Computer Organization and Architecture and their practical implementation. The developed calculator was tested for different arithmetic operations, and the results confirmed correct computation, proper control flow, and effective handling of division-by-zero conditions.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>RISC-V Architecture, RISC-V Assembly Language, Ripes Simulator, Computer Organization and Architecture, Processor Design, Low-Level Programming, ALU, Processor Simulation</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1hfLe6KGbGlD7gboo864LASzTJjMx7Tl8</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1FjUOKZotF-7gsnYUYB2_Dkd8IYFf4HQ9</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Dr.Sajitha A S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sreya Krishnan </t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>JEC24AD087</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>sreyakrishnan117@gmail.com</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Sreyas Mechinath Parambu</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>JEC24AD088</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Musthafa Nazar</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>JEC24AD062</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Anjana M</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>LJEC24AD094</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>IMG-20260815-WA0062 - 12417086 SREYA KRISHNAN.jpg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>IMG-20260815-WA0063 - 12417086 SREYA KRISHNAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46249.90108796296</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>johnsmaliyekalabraham.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Hotel Room Booking System</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>The hospitality industry relies heavily on efficient and reliable data management systems to handle daily activities such as room reservations, customer registration, billing, payment processing, and revenue tracking. Many small and medium-scale hotels still use manual records and spreadsheets, which can lead to data redundancy, inconsistent information, booking conflicts, billing errors, and inefficient reporting. These issues increase staff workload, reduce operational efficiency, and can negatively affect customer satisfaction.
+This paper presents the design and implementation of a relational database-driven Hotel Room Booking System using MySQL. The proposed system centralizes hotel operations through a structured relational database developed using Entity-Relationship (ER) modeling principles. The database is normalized up to Third Normal Form (3NF) to reduce data redundancy and prevent insertion, deletion, and update anomalies. Primary and foreign keys are used to maintain relationships between tables and ensure data consistency and referential integrity.
+The system follows a three-tier architecture consisting of presentation, application, and database layers. This structure improves modularity, scalability, and maintainability. SQL operations such as SELECT, INSERT, UPDATE, DELETE, and JOIN are used for efficient data manipulation and retrieval. These operations allow hotel staff to manage customers, rooms, reservations, billing information, and reports effectively.
+Transaction management and ACID properties ensure that important operations such as bookings and billing are completed reliably, even when multiple users access the system simultaneously. Database indexing is also used to improve query performance and speed up the retrieval of frequently accessed information.
+The evaluation of the proposed system demonstrates improved booking accuracy, prevention of double bookings, faster data retrieval, and effective enforcement of data integrity constraints. Overall, the Hotel Room Booking System demonstrates the practical application of DBMS concepts in the hospitality industry. By replacing inefficient manual processes with a centralized relational database, the system improves operational efficiency, data accuracy, customer service, and overall hotel management.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>AI, DBMS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1bfBU4Fiew41dvJux4BtpoqmkixZsR72P</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1LyePGUH1hONpdYt_0BuMbO2nicrdjFMG</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Jones Abraham</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>JEC24AD049</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>jonesmaliyakelabraham@gmail.com</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Job John</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>JEC24AD047</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Midhu Sunil</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>JEC24AD061</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Sreyas Mechinath</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>JEC24AD088</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>AI_Hotel_Room_Booking_Cover - 12417049 JONES MALIYAKEL ABRAHAM.jpg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Grand_Haven_Hotel - 12417049 JONES MALIYAKEL ABRAHAM.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46249.90492618056</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>keerthanamadhu.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air Quality Analysis using Machine Learning </t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Air pollution is a growing concern in urban environments, posing serious threats to
+public health and contributing to climate change. This project, titled “Air Quality
+Classification Using Machine Learning”, aims to develop a predictive model that classifies air
+quality into three health-relevant categories—Good, Moderate, and Poor—based on pollutant
+concentration data. The primary objective is to support public health awareness and enable
+data-driven environmental decision-making.The dataset used for this study, city_day.csv, was
+sourced from Kaggle and contains daily air quality records from multiple Indian cities. It
+includes 29,531 entries and 16 features, such as concentrations of PM2.5, PM10, NO, NO2,
+NOx, NH3, CO, SO2, O3, Benzene, Toluene, and Xylene, along with city and date
+information. Initial data exploration revealed approximately 18.73% missing values and the
+presence of outliers, necessitating thorough preprocessing.Data cleaning involved imputing
+missing numeric values using median and categorical values using mode, removing
+duplicates, standardizing date formats, and treating outliers using the IQR method. A new
+target variable, AQI_Bucket, was created by categorizing AQI values into Good, Moderate,
+and Poor. Categorical features were encoded using label encoding, and numerical features
+were scaled using Z-score normalization.Three machine learning models—K-Nearest
+Neighbors (KNN), Support Vector Machine (SVM), and Random Forest—were trained and
+evaluated. The Random Forest model achieved the highest accuracy of 87%, with AUC scores
+ranging from 0.95 to 0.98, indicating excellent classification performance. The final model
+allows users to input pollutant levels and receive real-time predictions of air quality
+status.This project aligns with Sustainable Development Goal 3 (Good Health and
+Well-being) by enabling predictive health risk modeling and SDG 13 (Climate Action) by
+supporting evidence-based climate policies. The outcome demonstrates how machine learning
+can be effectively applied to environmental data to promote healthier communities and
+sustainable urban planning.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine learning ,Artificial intelligence,Data science,Predictive analysis </t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1V7bXmR81RfeQhrnhG3rXTZPIy5S5gwJe</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1-kJ572yz1iY32pSe8t4097gY8PoE9Ff5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Dr.Parvathy Jyothi</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Keerthana Madhu </t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>JEC24AD055</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>keerthanamadhuu18@gmail.com</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Malavika P Santhosh</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>JEC24AD059</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Joel  V G</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>JEC24AD048</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Lal Krishna V J</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>JEC24AD058</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>IMG-20260815-WA0076 - 12417056 KEERTHANA MADHU.jpg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>IMG-20260815-WA0077 - 12417056 KEERTHANA MADHU.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46249.92086715278</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>aljona.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FOREST FIRE DETECTION </t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forest fires are a major environmental and economic threat, causing significant damage to forests, wildlife, and nearby communities. This project, “Forest Fire Detection,” aims to develop an intelligent system that automatically detects forest fires from images using deep learning. The system classifies images into two categories: Fire and No Fire, enabling early detection and rapid response.
+The project uses a Forest Fire Dataset containing over 5,000 images, covering both fire and non-fire scenarios. The images are preprocessed by removing duplicate and corrupted images, resizing them to 64×64 pixels, converting them to grayscale, normalizing pixel values, and assigning appropriate labels. Logistic Regression was implemented as a baseline model, while a Convolutional Neural Network (CNN) was developed as the primary deep learning model for classification.
+The CNN model was developed using TensorFlow and Keras and uses convolutional and pooling layers to automatically learn important visual features such as patterns, textures, and shapes. Data augmentation and dropout were used to improve model generalization and reduce overfitting. The model was evaluated using metrics such as accuracy, precision, recall, F1-score, confusion matrix, and ROC-AUC. The CNN demonstrated strong performance in distinguishing between fire and non-fire images.
+An alert mechanism was also integrated to notify users through a pop-up and email when fire is detected. The project demonstrates the potential of deep learning for automated environmental monitoring and early forest fire detection. Future improvements include real-time detection using camera or drone feeds, IoT-based monitoring, mobile application development, cloud deployment, and more advanced deep learning architectures.
+</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Python, CNN, Deep Learning, TensorFlow, Keras, Computer Vision, Machine Learning</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1yl8zNuyDscwiklEJ2fR_3d0KD3LyVPtd</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1vs2ywgMBgJAfXXVInP0h0CrrA6Z2tk5N</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ms. Divya Konikkara </t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ALJO N A</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>JEC24AD012</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>aljon9247@gmail.com</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>ABHIJITH NAMBIAR P</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>JEC24AD002</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>DEREK JHONY M</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>JEC24AD035</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>DEVIKA E V</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>JEC24AD036</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>image1 - 12417012 ALJO N A.png</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>prediction - 12417012 ALJO N A.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46249.93449887732</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>lloydsebastian.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mini Project</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>EchoScribe</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Therapists, counselors, and academic mentors spend
+too much time writing structured clinical records, which means
+they have less time to help the people they work with. We present
+EchoScribe, a platform that turns recorded two-party
+sessions into fully structured notes using a carefully planned
+pipeline of speech and language models. Unlike systems that
+hard-code specific AI providers, EchoScribe exposes a user-
+configurable provider chain: clinicians and developers supply
+their own API keys and select any supported model for each
+processing role, while the platform enforces an ordered multi-
+provider fallback policy at runtime. The backend currently
+supports models from the Gemini, Groq, and Deepgram families,
+with the provider-selection layer designed for straightforward
+extension to additional vendors. A separate Python microservice
+adds noise suppression based on SepFormer (trained on the
+WHAM! corpus) and speaker diarization based on ECAPA-
+TDNN (trained on VoxCeleb). Incoming audio is downsampled
+to 16 kHz mono and split into 1.5-second frames at a 0.75-
+second hop rate; cosine-similarity spectral clustering then puts
+each frame into one of two speakers. A lightweight eight-feature
+heuristic, combined with an LLM verification step, resolves
+the identities of the clinician and the client without needing
+prior speaker registration. Two documentation modes that work
+independently are provided: a Therapy pathway that automati-
+cally produces SOAP-structured notes and checks for language
+that suggests self-harm, and a Mentoring pathway that makes
+GROW-format notes and automatically signals when students are
+getting burned out. Reliability measures include a rotating multi-
+key provider pool, per-role fallback chains configurable through
+environment variables or a dashboard settings panel, endpoint-
+class rate caps ranging from 5 to 100 requests per minute, and
+per-row Supabase access policies. The system runs on Vercel
+with an optional Railway-hosted SpeechBrain service and handles
+sessions in twelve languages.
+</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>React, External AI, NLP, API,supabase</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=16Rb24qQ3qRntHzFvNSt2BEZ_eCwjJdkR</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1Fk6GqEtz6mp5ZpxyI6oPDboAx0bZbdT8</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>JAYAKRISHNAN A</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LLOYD SEBASTIAN </t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC23AD035 </t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://github.com/Lloydantonysebz</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANGISHA B </t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>JEC23AD013</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ARAVIND KRISHNAN S</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>JEC23AD018</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARVATHY KRISHNA M </t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>JEC23AD045</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>ChatGPT Image Aug 15, 2026, 09_36_19 PM - 12317035 LLOYD SEBASTIAN.png</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>ChatGPT Image Aug 15, 2026, 09_34_12 PM (1) - 12317035 LLOYD SEBASTIAN.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46249.93960820602</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>keerthanamadhu.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hospital Appointment Management System </t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>In the contemporary healthcare landscape, the transition from manual administrative 
+processes to automated digital systems is essential for improving operational efficiency and 
+patient care, as traditional paper-based methods often lead to significant bottlenecks such as 
+data redundancy, scheduling conflicts, and delayed access to medical services. This project 
+presents the design and implementation of a Hospital Appointment Management System 
+(HAMS), a database-centric application developed to streamline the scheduling lifecycle 
+through a robust Relational Database Management System (RDBMS). The system is 
+architected to manage four core entities—Patients, Doctors, Appointments, and 
+Departments—utilizing Entity-Relationship (ER) Modeling to map complex real-world 
+interactions into a structured digital format that prioritizes data consistency and logical 
+relationships. By leveraging SQL (Structured Query Language), the application ensures high 
+data quality and eliminates anomalies through rigorous Normalization, specifically achieving 
+Third Normal Form (3NF) to ensure that every non-key attribute is functionally dependent 
+only on the primary key.From a technical perspective, the project utilizes a 3-tier architecture, 
+ensuring a clean separation between the user interface, application logic, and the data storage 
+layer, which allows for scalable and secure data handling while enabling independent updates 
+to each layer without disrupting the entire system. A key technical achievement of the HAMS 
+is the enforcement of Referential Integrity Constraints and the use of unique composite keys 
+(combining Doctor ID, Date, and Time) to programmatically prevent double-booking, thereby 
+ensuring that doctor schedules remain synchronized and conflict-free. This implementation is
+further bolstered by the use of Data Definition Language (DDL) for robust schema creation 
+and Data Manipulation Language (DML) for efficient record retrieval and updates.
+Furthermore, the system incorporates complex JOIN operations and aggregate functions to 
+provide hospital administrators with real-time statistics on department loads and doctor 
+performance. Beyond mere operational efficiency, the implementation of this system 
+significantly reduces patient waiting times, minimizes administrative overhead, and provides 
+hospital staff with structured data insights for better resource allocation, ultimately 
+demonstrating how effective database management can transform a chaotic manual 
+environment into a reliable, high-performance, and paperless healthcare ecosystem that 
+prioritizes data security and user accessibility.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Database Management Systems (DBMS),   ​Polyglot Persistence ,  ​Healthcare Informatics / Hospital Information Systems   ,​Three-Tier Web Application Development  </t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1UA6IwVTjSiGtYUL1yLNAmzg3JnOb6VF0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1N8vhNWPdTXF-H6C0z2daZqSDJ15ikuCI</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Mr.Jithin K C</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Keerthana Madhu </t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>JEC24AD055</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>keerthanamadhuu18@gmail.com</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sreya Krishnan </t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>JEC24AD087</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> K P Adithya Dev </t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>JEC24AD056</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Krishanakumar E R</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>JEC24AD057</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>IMG-20260815-WA0103 - 12417056 KEERTHANA MADHU.jpg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>IMG-20260815-WA0125 - 12417056 KEERTHANA MADHU.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46249.95403194444</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>keerthanamadhu.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Stack and Function Call Mechanism Demo</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Stack and function call mechanisms are fundamental concepts in computer organization that 
+enable structured program execution and efficient memory management. In modern 
+computing systems, function calls rely heavily on stack-based operations to manage 
+parameters, return addresses, and local variables. This project presents a detailed study and 
+simulation-based understanding of stack operations and function call mechanisms at the 
+processor level.
+The system demonstrates how a stack operates using push and pop instructions, and 
+how function calls are implemented using stack frames. The project focuses on the working 
+of stack pointer (SP), frame pointer (FP), and program counter (PC) during function 
+invocation and return. It also highlights how recursion and nested function calls are handled 
+using stack memory. 
+A key feature of this project is the visualization of stack behavior during execution, 
+showing how data is stored and retrieved in a Last-In-First-Out (LIFO) manner. The 
+implementation ensures correct handling of function calls, return values, and stack overflow 
+conditions. 
+This project bridges the gap between theoretical concepts and practical understanding 
+by demonstrating how stack-based execution supports modular programming and efficient 
+control flow. It lays a strong foundation for understanding advanced topics such as memory 
+management, recursion, and compiler design.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer Organization and Architecture,   Low-Level Systems Programming and Assembly Language  , Memory Management and Data Structures   ,Processor Simulation and Microarchitectural Modeling   ,Compiler Design and Runtime Systems  </t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1m72Btyd8i0N7ZWAL7_Qh4qdP9N8zUJQF</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=17ObmganXeY_E-uKLILxkTSdI99buOX8o</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Dr.Sajitha A S</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Keerthana Madhu </t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>JEC24AD055</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>keerthanamadhuu18@gmail.com</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Nashwa Shirin K</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>JEC24AD063</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Samuel Shaju T</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>JEC24AD075</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Sankar M P</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>JEC24AD077</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>IMG-20260815-WA0130 - 12417056 KEERTHANA MADHU.jpg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>IMG-20260815-WA0132 - 12417056 KEERTHANA MADHU.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46249.96291405093</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>hibarebink.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Main Project</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NexTeX: Smart Academic Writing Assistant</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>LaTeX remains the gold standard for academic and scientific typesetting, yet its steep
+learning curve and cryptic error handling often hinder productivity. NexTeX proposes a
+next-generation, AI-enhanced LaTeX editor designed to simplify academic writing and
+publishing. The system integrates four core innovations: (1) an AI-powered Debugging
+Assistant that translates compiler errors into human-readable explanations with
+actionable fixes, (2) an Automated Data-to-Typeset Module that converts raw datasets
+(CSV/Excel) into professionally formatted LaTeX tables using intelligent data
+processing, (3) a Plagiarism Detection Module that leverages natural language
+processing and similarity analysis to ensure originality in academic writing, and (4) a
+Smart Report &amp; Journal Paper Generator that provides ready-to-use templates for
+academic reports and journal submissions, complete with automated citation formatting
+and compliance with publication standards. By combining natural language processing,
+data automation, plagiarism detection, and structured template generation, NexTeX
+bridges the gap between complex typesetting and user-centric academic workflows.
+This project aims to empower students, researchers, and faculty to focus on content
+creation and originality rather than technical barriers, thereby redefining the future of
+academic publishing</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Django, HTML5, CSS, Python, SQL, JavaScript</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1AHHUw2WIMdocTVQXezQuPDxzFf8b_Fg2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1fZbntUunff15MBfcYdB30aNM0Cag2KQ6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Ms. LINTA AT</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Hiba Rebin K</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC23AD029 </t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hibarebink.ad23@jecc.ac.in </t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Irine Vincent</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>JEC23AD030</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Muhammed Shiyas M</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC23AD041 </t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Pavan R Kumar</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>JEC23AD046</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>IMG-20260815-WA0124 - 12317029 HIBA REBIN K.jpg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>IMG-20260815-WA0111 - 12317029 HIBA REBIN K.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46249.98369782407</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>pavandass.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Machine-Learning based student information system featuring equitable scholarship recommendation.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The "Student Information System (SIS)" is a web-based database management application developed to efficiently manage and centralize academic information within an educational institution. The system replaces conventional manual record-keeping methods with a structured digital platform for maintaining student details, teacher information, course enrollments, attendance records, and academic grades. It provides a centralized interface through which authorized users can add, view, update, and delete records while ensuring consistency and reducing data redundancy.
+The system is implemented using "PHP, MySQL, HTML, and CSS", with "XAMPP" providing the local server environment. The database follows a relational model in which entities such as Students, Teachers, Courses, Enrollments, Attendance, and Grades are interconnected using primary and foreign keys. Database normalization, particularly **Third Normal Form (3NF)**, is applied to minimize redundancy and prevent insertion, deletion, and update anomalies. Referential integrity constraints ensure that relationships between related records remain consistent.
+The system includes modules for "student management, teacher management, course management, enrollment, attendance tracking, and grade management", along with a centralized dashboard and role-based login functionality. Attendance records can be monitored through course-wise and student-wise information, while academic performance can be reviewed through the grades module.
+As an extended feature, the project incorporates an "AI-assisted scholarship recommendation concept" that considers academic performance, attendance, financial need, and related student information to prioritize scholarship opportunities. The system also provides provisions for "emergency financial support and document verification", allowing teachers or authorized personnel to review and verify student information before making support-related decisions.
+Overall, the project demonstrates how a relational database combined with a web-based interface can provide a reliable, organized, and scalable solution for academic information management. The system improves accessibility, reduces manual effort, supports data integrity, and provides a foundation for future integration of advanced analytics and intelligent student-support services.
+</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>DBMS, MySQL, SQL, PHP, HTML/CSS, AI/ML</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1KJ51X_DzLLEjXmKjclhwJ1rgw7qdy-Yc</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1Xzv6zo5bbH8zk-cpTYscwBFLoQrnsAT0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>PAVANDAS S</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>JEC24AD070</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>pavanarikkinchira@gmail.com</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>REVATHI G R</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>JEC24AD072</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>ANJANA M</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>LJEC24AD094</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>NANDITHA MADHAVAN CM</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>LJEC24AD095</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>SIS_Project_Cover_Image - 12417070 PAVANDAS S.png</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Screenshot 2026-08-15 232300 - 12417070 PAVANDAS S.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46250.02791896991</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>aishwaryadineshrao.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mini Project</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>INTELLIGENT DECEPTION DETECTION USING VISUAL AND PHYSIOLOGICAL SIGNAL FUSION</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>This project proposes an intelligent software system for analyzing eye movement patterns and pulse rate variations to assist in lie detection and guilt assessment during criminal investigations. The system combines hardware-based sensing with artificial intelligence to capture and analyze real-time physiological and behavioral signals.
+The hardware setup uses an Arduino microcontroller integrated with a MAX30102 pulse sensor to continuously monitor the subject’s heart rate. The collected pulse signals are transmitted to a computer through serial communication for further processing. At the same time, a camera-based eye-tracking module captures behavioral features such as eye movements, blink rate, gaze direction, and fixation patterns.
+The acquired multi-modal data is preprocessed to reduce noise and normalized using baseline readings collected during an initial calibration phase. Machine learning models are then used to extract meaningful features, including heart rate variations, heart rate variability, abnormal pulse fluctuations, irregular eye movements, and changes in blink frequency. These features are analyzed to identify patterns related to stress, cognitive load, and behavioral anomalies that may occur during deceptive responses.
+By correlating physiological and visual signals with responses to structured questions, the system generates a deception likelihood score and an estimated guilt probability. The integration of Arduino-based sensing, real-time signal processing, and machine learning enables a cost-effective and scalable solution.
+The proposed system is intended as a technology-driven decision-support tool for investigative applications. It can help reduce dependence on subjective observations, improve consistency in interrogation analysis, and demonstrate the potential of combining embedded systems and artificial intelligence for human behavior analysis.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Python, Machine Learning, Deep Learning, CNN, Random Forest, Computer Vision, OpenCV, Arduino, IoT, Signal Processing</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1x0ktBCrcLIYPfMBPGo-nY7lC7VQUjV3_</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1_m3ILRwSoFxcc02DO-iqqKD9y_xu3tkt</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Dr. Anoop V</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Aishwarya Dinesh Rao</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>JEC23AD005</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>aishwaryadineshrao.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Abirami S</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>JEC23AD003</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Alet Jose</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>JEC23AD009</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Aneesh V</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>JEC23AD012</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>deception_detection_cover_1MB - 12317005 AISHWARYA DINESH RAO.jpg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>IMG_1984 - 12317005 AISHWARYA DINESH RAO.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46250.3062746412</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>fahadaboobeckar.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PASSWORD VERIFICATION SYSTEM</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>The Password Verification System is a micro project developed using RISC-V assembly language and simulated in the RIPES environment. The system verifies whether a user-entered password matches a predefined password stored in memory and provides appropriate access responses. The implementation demonstrates fundamental concepts of Computer Organization and Architecture such as instruction execution, memory access, register operations, branching, and pipelining. The program compares passwords character by character using RISC-V instructions including LB, BEQ, and BNE. If all characters match, the system displays "Access Granted"; otherwise, it displays "Access Denied". The RIPES simulator enables visualization of processor activities such as register updates, instruction flow, memory interactions, and pipeline execution. This project helps students understand how authentication mechanisms are implemented at the processor level while gaining practical experience with low-level programming and RISC-V architecture. It bridges theoretical concepts with real-world implementation and provides a foundation for further learning in embedded systems, processor design, and secure computing applications.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>RISC-V Architecture, Assembly Language Programming, RIPES Simulator, Computer Organization &amp; Architecture, Processor Pipelining, Memory Management, Authentication System Design</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1HRGq22XlbBGkgWAOMScGbq80T0Fe0tyr</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1j6aggRzGC6ln7_e9ntjPivM3IttGRm9m</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Dr. Sandeep C S</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>FAHAD ABOOBACKER N S</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>JEC24AD039</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Fahadns</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>ABIEAL JOBY</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>JEC24AD004</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>ARYA K A</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>JEC24AD023</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>FATHIMA MISNA T E</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>JEC24AD041</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>password_verification_cover_under_1MB - 12417039 FAHAD ABOOBACKER N S.jpg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>AISelect_20260816_070659_Drive - 12417039 FAHAD ABOOBACKER N S.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46250.36234203703</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>anjubiju.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Student Performance Prediction</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>The Student Performance Prediction project uses machine learning techniques to analyze student academic, demographic, and behavioral factors that influence academic performance. The project aims to identify patterns in student data and predict student performance using a machine learning classification model. The dataset contains 1000 student records with features related to gender, parental education, lunch type, test preparation, and subject scores. Data preprocessing techniques such as data cleaning, categorical encoding, missing-value checking, duplicate detection, and feature scaling are performed to prepare the dataset for model training. Exploratory Data Analysis is carried out using histograms, countplots, boxplots, and correlation heatmaps to understand patterns and relationships in the data. Logistic Regression is used as the machine learning model for prediction, and its performance is evaluated using accuracy, confusion matrix, and ROC curve. The project demonstrates how data science and machine learning can support educational decision-making and help identify students who may need additional academic support.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Data Science, Machine Learning, Python, Pandas, NumPy, Scikit-learn, Matplotlib, Seaborn</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1sUpfqah9MXUPFqd66HiW4o2FGuNb5VoW</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1dVq62SEbs9foEx8ExgJj1x16bBnPkAnz</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Divya konikkara </t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anju Biju </t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>JEC24AD018</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>anjubiju229@gmail.com</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Athul K K</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>JEC24AD027</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Basil K David</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>JEC24AD032</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Isha Fathima</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>JEC24AD045</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>IMG_20260816_083943 - 12417018 ANJU BIJU.png</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>IMG_20260816_083955 - 12417018 ANJU BIJU.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46250.37139797454</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>anjubiju.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Pipeline Hazard Detection and Resolution</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Instruction pipelining is an important technique used in modern processors to improve performance by allowing multiple instructions to be processed simultaneously through different pipeline stages. However, the smooth execution of instructions can be affected by conflicts known as pipeline hazards. These hazards may occur because of dependencies between instructions, limited hardware resources, or changes in program control flow.
+This project, titled “Pipeline Hazard Detection and Resolution,” focuses on studying the different types of pipeline hazards and the techniques used to detect and resolve them in a pipelined processor. The major types of hazards considered in this project are structural hazards, data hazards, and control hazards. The project analyzes how these hazards affect instruction execution and processor performance.
+The project also studies the role of the Hazard Detection Unit (HDU) in identifying conflicts between instructions. Various hazard resolution techniques, including pipeline stalling, data forwarding (bypassing), and branch handling, are explored to reduce delays and improve pipeline efficiency.
+For practical demonstration, the project uses the Ripes RISC-V processor simulator. RISC-V assembly programs containing instruction dependencies and branch instructions are executed in the simulator. The pipeline execution is observed through the pipeline diagram to identify hazards, stalls, forwarding, and changes in instruction flow.
+The project provides both theoretical and practical understanding of pipeline hazards and their resolution. The simulation demonstrates how proper hazard detection and resolution can reduce pipeline delays and improve the efficiency of instruction execution. This study provides a foundation for understanding the internal operation of modern pipelined processors and the techniques used to achieve better processor performance.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>RISC-V, Ripes, Assembly Language, Instruction Pipelining, Computer Architecture</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=16EnvIrnHJQjEvA0vAmRqwRlp4zDeJqwv</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=103A7PWh32GgQeiFgR4Ue_-e6IZn6Y-bd</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Dr.Sandeep C S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anju Biju </t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>JEC24AD018</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>anjubiju229@gmail.com</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Aman K R</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>JEC24AD013</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bilal V </t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>JEC24AD033</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Devika E V</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>JEC24AD036</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>IMG_20260816_085304 - 12417018 ANJU BIJU.png</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>IMG_20260816_085333 - 12417018 ANJU BIJU.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46250.40698865741</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>josephkbabu.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DIGITAL DICE ROLLER MECHANISM DEMO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>This project introduces an innovative software-centric approach by designing and simulating a digital dice roller utilizing the RISC-V Instruction Set Architecture (ISA), which offers a flexible and modern solution to basic random generation challenges. Conducted within the Ripes simulator environment, this endeavor demonstrates the efficacy of employing fundamental processor instructions to govern simulated pseudo-random systems, specifically focusing on dice rolls. The design leverages general-purpose registers to accurately compute the operational states of the generated numbers one, through, to six while implementing software-defined math to establish precise modular scaling. This approach facilitates a continuous and deterministic pseudo random sequence that can adapt in real-time to varying software constraints. By allowing for software-defined mathematical configurations, this methodology not only enhances flexibility but simplifies modifications, thereby enabling software engineers to respond swiftly to bounds without the need for extensive hardware additions.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Assembly Language</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1uK3DxrLW9rlw7kEkMGJWWw3kyB7osKdQ</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1qbvuCw0NOKBc0T_hWKYDfAaWZbSJylRL</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Dr. Sajitha A S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joseph K Babu </t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>JEC24AD051</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>josephkbabu.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Joel V G</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>JEC24AD048</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nithali Chandran</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>JEC24AD067</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Oshly Jopko</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>JEC24AD068</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>1000085928 - 12417051 JOSEPH K BABU.png</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Screenshot_2026_0816_094115 - 12417051 JOSEPH K BABU.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46250.41173712963</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>nithalichandran.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Water Quality Prediction</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Water Quality Prediction is a data-driven machine learning project developed to predict whether a water sample is safe for human consumption. Water quality monitoring is important for protecting public health and ensuring sustainable management of water resources. The project focuses on analysing physicochemical properties of water and classifying samples as potable (safe) or non-potable (unsafe).
+The dataset used in the project was obtained from Kaggle and contains 3,276 rows and 10 columns, consisting of nine input features: pH, hardness, solids, chloramines, sulphate, conductivity, organic carbon, trihalomethanes, and turbidity, along with the target variable, potability. Data preprocessing was performed to improve the quality and suitability of the dataset for machine learning. Missing values were replaced using median imputation, duplicate records were checked, and outliers were capped using the Interquartile Range (IQR) method. The numerical features were standardized using StandardScaler, and SMOTE (Synthetic Minority Over-sampling Technique) was applied to address class imbalance.
+Exploratory Data Analysis was carried out using histograms, box plots, correlation analysis, and a heatmap to understand feature distributions and relationships. Two machine learning algorithms, Random Forest Classifier and XGBoost Classifier, were implemented and evaluated. The Random Forest model achieved an accuracy of approximately 66%, while XGBoost achieved 62%. Based on accuracy, stability, and interpretability, Random Forest was selected as the final model. Evaluation was performed using accuracy, confusion matrix, precision, recall, F1-score, and ROC-AUC.
+The project demonstrates the potential of machine learning for automated water quality assessment and data-driven decision-making. It contributes to SDG 3 (Good Health and Well-being) and SDG 6 (Clean Water and Sanitation) by supporting the identification of potentially unsafe water sources. Future improvements include using larger datasets, real-time IoT sensor data, advanced machine learning techniques, feature engineering, and developing a web or mobile application for real-time water potability prediction.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (AI), Data Science, Machine Learning, Python, Pandas, NumPy, Scikit-learn, Random Forest, XGBoost, SMOTE</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1HGVBtDbo0OEnSEPGYs8spVDiD9S4oA1x</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=12aC1y_7UXNKWhsgVQ7nKn-2rvgzLm8Dd</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Parvati Jyothi</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Nithali Chandran</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>JEC24AD067</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Sreelakshmi P</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>JEC24AD086</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sankar M P</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>JEC24AD077</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Adharsh Krishna P M</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>LJEC24AD093</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>IMG_2604 - 12417067 NITHALI CHANDRAN.png</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>IMG_2606 - 12417067 NITHALI CHANDRAN.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46250.42203997685</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ameyajosechazhoor.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SOIL-QUALITY-PREDICTION-AND-CROP-RECOMMENTATION</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Soil Quality Predictor &amp; Crop Recommendation System
+This project is a machine learning-based web application designed to recommend the most suitable crop based on soil and environmental parameters. The system analyzes parameters such as Nitrogen (N), Phosphorus (P), Potassium (K), temperature, humidity, pH, and rainfall to predict an appropriate crop for the given conditions.
+The project uses a trained machine learning classification model and provides an easy-to-use web interface where users can enter soil and environmental values and receive a crop recommendation. The system demonstrates an end-to-end machine learning workflow including data preprocessing, model training, prediction, and deployment through a web application.
+The main objective of the project is to support data-driven agricultural decision-making by helping users identify crops that are better suited to specific soil and climatic conditions.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Machine Learning, Python, Streamlit, Scikit-learn, Pandas, NumPy</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1EdwRhoyZMb8r782e1ZfGus75a3g8zSOj</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1ucQxNFHZr-9M2-_wSqRUxQud98zyhZC-</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Divya Konikkara</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ameya Jose Chazhoor </t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>JEC24AD014</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>ameyajose2020@gmail.com, https://github.com/amkbitshift/SOIL-QUALITY-PREDICTION-AND-CROP-RECOMMENTATION</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anu V Nair </t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>JEC24AD021</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gowri Sooraj </t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>JEC24AD042</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cherian Aby Elenjikal </t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>JEC24AD034</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Gemini_Generated_Image_khrynakhrynakhry (1) - 12417014 AMEYA JOSE CHAZHOOR.png</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-08-16 at 9.58.26 AM - 12417014 AMEYA JOSE CHAZHOOR.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46250.43051572917</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ameyajosechazhoor.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Calculator Implementation Using RISC-V Simulator</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Calculator Implementation Using RISC-V Simulator
+This project implements a basic calculator using RISC-V assembly language and a RISC-V simulator. The project demonstrates the practical application of Computer Organization and Architecture concepts by implementing arithmetic operations at the instruction-set level.
+The calculator accepts numerical inputs and performs fundamental arithmetic operations such as addition, subtraction, multiplication, and division using RISC-V instructions. The program is executed and tested using a RISC-V simulator, allowing the execution of instructions, register operations, memory usage, and program flow to be observed.
+The main objective of the project is to understand how high-level arithmetic operations are translated into low-level assembly instructions and executed by a processor architecture. The project provides practical exposure to RISC-V instruction sets, registers, arithmetic and logical operations, branching, and program control.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Computer Organization and Architecture, RISC-V, RISC-V Assembly, RARS Simulator</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1MajYNkyeFTBkg_yEfAtqRQcoGe4FYa7J</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1Ovc4t1smD_KjKzw5W1c_gxkPSpXk9BWb</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Sandeep</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Ameya Jose Chazhoor</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>JEC24AD014</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>ameyajose2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Anand G K</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>JEC24AD015</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ashlin Theres James</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>JEC24AD024</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Gemini_Generated_Image_fu181kfu181kfu18 (1) - 12417014 AMEYA JOSE CHAZHOOR.png</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-08-16 at 10.14.26 AM - 12417014 AMEYA JOSE CHAZHOOR.jpeg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/Academic Projects.xlsx
+++ b/public/Academic Projects.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +57,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y32"/>
+  <dimension ref="A1:Y75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,7 +560,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>46248.92346111111</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Mr. Shine P Xavier</t>
+          <t>Shine P Xavier</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -654,25 +654,11 @@
       <c r="S2" t="inlineStr">
         <is>
           <t>JEC23AD007</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>hireflow 1 - 12317004 ADHITHYAN V V.png</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>hireflow 2 - 12317004 ADHITHYAN V V.png</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>46248.93052409722</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -718,7 +704,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Anjali</t>
+          <t>Anjali O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -764,25 +750,11 @@
       <c r="S3" t="inlineStr">
         <is>
           <t>JEC25AD029</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>IMG-20260814-WA0132 - 12517006 ADHARSH SATHEESH KUMAR.jpg</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>IMG-20260814-WA0137 - 12517006 ADHARSH SATHEESH KUMAR.jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>46249.48421563658</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -828,7 +800,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Dr Sajitha A S</t>
+          <t>Sajitha A S</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -864,27 +836,11 @@
       <c r="Q4" t="inlineStr">
         <is>
           <t>JEC23AD053</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>IMG-20260806-WA0041 - 12317028 GRACE MARIA REJI.jpg</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Screenshot_20260815_113530_WhatsApp - 12317028 GRACE MARIA REJI.jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>46249.60343123843</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -933,7 +889,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Divya konikkara</t>
+          <t>Divya Konikkara</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -979,25 +935,11 @@
       <c r="S5" t="inlineStr">
         <is>
           <t>JEC24AD028</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>fraud_detection_explainable_ai_cover_under_1mb - 12417004 ABIEAL JOBY.jpg</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>fraud_detection_working_demo_under_1mb - 12417004 ABIEAL JOBY.jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>46249.64578863426</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1076,7 +1018,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Dr.sajitha A S</t>
+          <t>Sajitha A S</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1112,27 +1054,11 @@
       <c r="Q6" t="inlineStr">
         <is>
           <t>JEC23AD053</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>AI_Language_Learning_AR_Cover_Under_1MB-8 - 12317028 GRACE MARIA REJI.jpg</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>IMG-20260316-WA0029 - 12317028 GRACE MARIA REJI.jpg</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>46249.82735542824</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1200,7 +1126,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Dr. Sandeep C S</t>
+          <t>Sandeep C S</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1246,25 +1172,11 @@
       <c r="S7" t="inlineStr">
         <is>
           <t>JEC24AD017</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>memory_system_cover_under_1MB - 12417007 AISWARYA KALLAYIL RAJESH.jpg</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>project_working_demo_under_1MB - 12417007 AISWARYA KALLAYIL RAJESH.jpg</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>46249.8493425</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1355,25 +1267,11 @@
       <c r="S8" t="inlineStr">
         <is>
           <t>JEC24AD086</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>IMAGE (3) - 12417077 SEANNA K S.png</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>IMAGE (2) - 12417077 SEANNA K S.png</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>46249.85844240741</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1437,7 +1335,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Ms. LINTA AT</t>
+          <t>Linta A T</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1483,25 +1381,11 @@
       <c r="S9" t="inlineStr">
         <is>
           <t>JEC23AD046</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>IMG-20260815-WA0023 - 12317029 HIBA REBIN K.jpg</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>IMG-20260815-WA0069 - 12317029 HIBA REBIN K.jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>46249.86108936342</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1546,7 +1430,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Ms. Divya Konikkara</t>
+          <t>Divya Konikkara</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1592,25 +1476,11 @@
       <c r="S10" t="inlineStr">
         <is>
           <t>JEC24AD044</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>driver detection image - 12417003 ABHINAV S K.jpeg</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Driver_Drowsiness_Working_Demo - 12417003 ABHINAV S K.png</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>46249.87296578704</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1657,7 +1527,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Ms. Divya Konikkara</t>
+          <t>Divya Konikkara</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1693,27 +1563,11 @@
       <c r="Q11" t="inlineStr">
         <is>
           <t>JEC24AD016</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>AI image - 12417030 AYSHA SHAFEEK.jpg</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>project demo - 12417030 AYSHA SHAFEEK.jpeg</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>46249.88104824074</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1758,7 +1612,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Dr. Sandeep C S</t>
+          <t>Sandeep C S</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1794,27 +1648,11 @@
       <c r="Q12" t="inlineStr">
         <is>
           <t>JEC24AD042</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>coa image - 12417003 ABHINAV S K.jpeg</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>COA_RIPES_Figure_Working_Demo - 12417003 ABHINAV S K.jpg</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>46249.88267362268</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1859,7 +1697,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Jithin KC</t>
+          <t>Jithin K C</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1895,27 +1733,11 @@
       <c r="Q13" t="inlineStr">
         <is>
           <t>JEC24AD064</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Screenshot_20260815-205945 - 12417054 KEERTHANA B.png</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Screenshot_20260815-210147 - 12417054 KEERTHANA B.png</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>46249.89212006945</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,7 +1806,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Jithin K.C</t>
+          <t>Jithin K C</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2030,25 +1852,11 @@
       <c r="S14" t="inlineStr">
         <is>
           <t>JEC24AD075</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>IMG-20260815-WA0045 - 12417075 SANA FATHIMA P B.jpg</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>IMG-20260815-WA0051 - 12417075 SANA FATHIMA P B.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>46249.8932746875</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -2101,7 +1909,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Dr.Parvathy Jyothi</t>
+          <t>Jithin K C</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2147,25 +1955,11 @@
       <c r="S15" t="inlineStr">
         <is>
           <t>LJEC24AD095</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Road-accident - 12417086 SREYA KRISHNAN.jpeg</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Demo - 12417086 SREYA KRISHNAN.jpeg</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>46249.89956996528</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -2214,7 +2008,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Dr.Sajitha A S</t>
+          <t>Sajitha A S</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2260,25 +2054,11 @@
       <c r="S16" t="inlineStr">
         <is>
           <t>LJEC24AD094</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>IMG-20260815-WA0062 - 12417086 SREYA KRISHNAN.jpg</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>IMG-20260815-WA0063 - 12417086 SREYA KRISHNAN.jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>46249.90108796296</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -2375,23 +2155,9 @@
           <t>JEC24AD088</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>AI_Hotel_Room_Booking_Cover - 12417049 JONES MALIYAKEL ABRAHAM.jpg</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Grand_Haven_Hotel - 12417049 JONES MALIYAKEL ABRAHAM.jpg</t>
-        </is>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>46249.90492618056</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -2460,7 +2226,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Dr.Parvathy Jyothi</t>
+          <t>Jithin K C</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2506,25 +2272,11 @@
       <c r="S18" t="inlineStr">
         <is>
           <t>JEC24AD058</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>IMG-20260815-WA0076 - 12417056 KEERTHANA MADHU.jpg</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>IMG-20260815-WA0077 - 12417056 KEERTHANA MADHU.jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>46249.92086715278</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -2573,7 +2325,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ms. Divya Konikkara </t>
+          <t>Divya Konikkara</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2619,25 +2371,11 @@
       <c r="S19" t="inlineStr">
         <is>
           <t>JEC24AD036</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>image1 - 12417012 ALJO N A.png</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>prediction - 12417012 ALJO N A.jpg</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>46249.93449887732</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -2716,7 +2454,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>JAYAKRISHNAN A</t>
+          <t>Jayakrishnan A</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2762,25 +2500,11 @@
       <c r="S20" t="inlineStr">
         <is>
           <t>JEC23AD045</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>ChatGPT Image Aug 15, 2026, 09_36_19 PM - 12317035 LLOYD SEBASTIAN.png</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>ChatGPT Image Aug 15, 2026, 09_34_12 PM (1) - 12317035 LLOYD SEBASTIAN.png</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>46249.93960820602</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -2854,7 +2578,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Mr.Jithin K C</t>
+          <t>Jithin K C</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2900,25 +2624,11 @@
       <c r="S21" t="inlineStr">
         <is>
           <t>JEC24AD057</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>IMG-20260815-WA0103 - 12417056 KEERTHANA MADHU.jpg</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>IMG-20260815-WA0125 - 12417056 KEERTHANA MADHU.jpg</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>46249.95403194444</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -2981,7 +2691,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Dr.Sajitha A S</t>
+          <t>Sajitha A S</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3027,25 +2737,11 @@
       <c r="S22" t="inlineStr">
         <is>
           <t>JEC24AD077</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>IMG-20260815-WA0130 - 12417056 KEERTHANA MADHU.jpg</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>IMG-20260815-WA0132 - 12417056 KEERTHANA MADHU.jpg</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>46249.96291405093</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -3106,7 +2802,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Ms. LINTA AT</t>
+          <t>Linta A T</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3152,25 +2848,11 @@
       <c r="S23" t="inlineStr">
         <is>
           <t>JEC23AD046</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>IMG-20260815-WA0124 - 12317029 HIBA REBIN K.jpg</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>IMG-20260815-WA0111 - 12317029 HIBA REBIN K.jpg</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>46249.98369782407</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -3268,23 +2950,9 @@
           <t>LJEC24AD095</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>SIS_Project_Cover_Image - 12417070 PAVANDAS S.png</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Screenshot 2026-08-15 232300 - 12417070 PAVANDAS S.png</t>
-        </is>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>46250.02791896991</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -3333,7 +3001,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Dr. Anoop V</t>
+          <t>Anoop V</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3379,25 +3047,11 @@
       <c r="S25" t="inlineStr">
         <is>
           <t>JEC23AD012</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>deception_detection_cover_1MB - 12317005 AISHWARYA DINESH RAO.jpg</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>IMG_1984 - 12317005 AISHWARYA DINESH RAO.jpeg</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>46250.3062746412</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -3442,7 +3096,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Dr. Sandeep C S</t>
+          <t>Sandeep C S</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3488,25 +3142,11 @@
       <c r="S26" t="inlineStr">
         <is>
           <t>JEC24AD041</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>password_verification_cover_under_1MB - 12417039 FAHAD ABOOBACKER N S.jpg</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>AISelect_20260816_070659_Drive - 12417039 FAHAD ABOOBACKER N S.jpg</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>46250.36234203703</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -3551,7 +3191,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Divya konikkara </t>
+          <t>Divya Konikkara</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3597,25 +3237,11 @@
       <c r="S27" t="inlineStr">
         <is>
           <t>JEC24AD045</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>IMG_20260816_083943 - 12417018 ANJU BIJU.png</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>IMG_20260816_083955 - 12417018 ANJU BIJU.png</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>46250.37139797454</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -3664,7 +3290,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Dr.Sandeep C S</t>
+          <t>Sandeep C S</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3710,25 +3336,11 @@
       <c r="S28" t="inlineStr">
         <is>
           <t>JEC24AD036</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>IMG_20260816_085304 - 12417018 ANJU BIJU.png</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>IMG_20260816_085333 - 12417018 ANJU BIJU.png</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>46250.40698865741</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -3773,7 +3385,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Dr. Sajitha A S</t>
+          <t>Sajitha A S</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3819,25 +3431,11 @@
       <c r="S29" t="inlineStr">
         <is>
           <t>JEC24AD068</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>1000085928 - 12417051 JOSEPH K BABU.png</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Screenshot_2026_0816_094115 - 12417051 JOSEPH K BABU.png</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>46250.41173712963</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -3886,7 +3484,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Parvati Jyothi</t>
+          <t>Jithin K C</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3932,25 +3530,11 @@
       <c r="S30" t="inlineStr">
         <is>
           <t>LJEC24AD093</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>IMG_2604 - 12417067 NITHALI CHANDRAN.png</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>IMG_2606 - 12417067 NITHALI CHANDRAN.png</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>46250.42203997685</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -4046,23 +3630,9 @@
           <t>JEC24AD034</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Gemini_Generated_Image_khrynakhrynakhry (1) - 12417014 AMEYA JOSE CHAZHOOR.png</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>WhatsApp Image 2026-08-16 at 9.58.26 AM - 12417014 AMEYA JOSE CHAZHOOR.jpeg</t>
-        </is>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>46250.43051572917</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -4110,7 +3680,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Sandeep</t>
+          <t>Sandeep C S</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4148,20 +3718,4257 @@
           <t>JEC24AD024</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Gemini_Generated_Image_fu181kfu181kfu18 (1) - 12417014 AMEYA JOSE CHAZHOOR.png</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>WhatsApp Image 2026-08-16 at 10.14.26 AM - 12417014 AMEYA JOSE CHAZHOOR.jpeg</t>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>46250.5091278125</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>malavikapsanthosh.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single cycle processors vs pipelined professor </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This project presents a comparative study of a Single Cycle Processor and a 5-Stage Pipelined Processor using the RISC-V RV32I instruction set and the Ripes microarchitectural simulator. Processor architecture plays an important role in determining execution speed, throughput, hardware utilization, and overall computational efficiency.
+In the Single Cycle architecture, each instruction completes all five major stages—Instruction Fetch (IF), Instruction Decode (ID), Execute (EX), Memory Access (MEM), and Write Back (WB)—within a single clock cycle. Although this approach is simple and easy to understand, the clock cycle must accommodate the slowest instruction, resulting in lower throughput. In contrast, the 5-Stage Pipelined Processor divides instruction execution into separate stages and allows multiple instructions to overlap, improving instruction throughput and resource utilization.
+As a practical implementation, an array summation program is developed using RISC-V assembly instructions such as lw, add, addi, beq, j, and sw. The same program is executed on both processor architectures using the Ripes simulator. The project observes instruction flow, register updates, datapath activity, clock cycles, and execution behaviour to understand the architectural differences.
+The study demonstrates that pipelining can significantly improve processor performance through instruction-level parallelism, while also introducing challenges such as data hazards, control hazards, stalls, and additional control complexity. The project therefore highlights the trade-off between the simplicity of Single Cycle architecture and the improved performance and efficiency of Pipelined architecture.
+Overall, the project bridges theoretical concepts of Computer Organization and Architecture with practical processor simulation, providing a clear understanding of RISC-V instruction execution, datapath organization, pipeline behaviour, and performance optimization.
+</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1.Computer Organization and Architecture,Processor Design and Microarchitecture ,RISC-V Architecture and Assembly Programming, Pipeline Processing and Performance Analysis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1R3QCYMHWpxonrpViVIe--sm84GOpBtjW</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1nogzKAUL1_05GmqeXD3VQ3c3ZsIHLYoc</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sajitha A S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Krishnakumar E R</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>JEC24AD057</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>malavikapsanthosh55@gmail.com</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Ravathi G R</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>JEC24AD072</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Shiyon Josy V</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>JEC24AD081</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Malavika P Santhosh </t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC24AD059 </t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>46250.51747212963</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>saniyaashraf.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Main Project</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>A Smart Healthcare Management System with Voice-Assisted Medication Alerts, Appointment Scheduling, Disease Prediction, and Secure Encrypted Data Storage for Alzheimer’s Care</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The increasing demand for efficient healthcare services and personalized patient care has accelerated the adoption of intelligent digital healthcare solutions. Healthcare institutions face significant challenges in managing hospital staff, maintaining patient records, ensuring medication adherence, and protecting sensitive medical information. Alzheimer's patients, in particular, require continuous monitoring due to memory impairment, which often leads to missed medications, forgotten appointments, and delayed medical attention. To address these challenges, this project proposes an AI-Driven Smart Healthcare Management System with Voice-Assisted Medication Alerts, Appointment Scheduling, Disease Prediction, and Secure Encrypted Data Storage for Alzheimer's Care. The proposed system integrates a web-based Healthcare Staff Management System with an Android-based mobile application to provide a unified healthcare platform. The web application enables efficient management of healthcare professionals through role-based access control, staff registration, department allocation, attendance tracking, duty scheduling, and leave management, thereby improving hospital administration and resource utilization. The Android application is designed to support Alzheimer's patients by providing voice-assisted medication reminders, appointment notifications, medicine intake confirmation, and caregiver communication, promoting better treatment adherence and independent patient care. The system incorporates Artificial Intelligence (AI) techniques to analyze patient medical history and healthcare data for disease prediction, assisting healthcare professionals in making timely and informed clinical decisions. To further enhance privacy and collaborative learning, Federated Learning is considered for decentralized model training, enabling AI models to learn from distributed healthcare data without exposing sensitive patient information. Additionally, all critical healthcare records, including patient details, medication schedules, appointment information, and caregiver notes, are protected using Advanced Encryption Standard (AES) encryption to ensure confidentiality, integrity, and secure access. The proposed solution aims to create an intelligent, secure, and scalable healthcare ecosystem that integrates hospital administration with patient-centric assistance. By combining AI-driven analytics, voice-enabled support, secure data management, and intelligent automation, the system is expected to improve healthcare efficiency, reduce human error, enhance medication compliance, strengthen patient safety, and support better clinical decision-making for modern healthcare environments. </t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>AI, Machine Learning, Python Flask, MySQL, AES Encryption, Federated Learning, FCM, Text-to-Speech (TTS)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=13SpYwMe_A0SN0yx9KKPf9TPLG0VkaRz6</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=16Ut83z6dS2TwmN_dFMlEzvrFiQyvGbfk</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Anjali O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Saniya Ashraf</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>JEC23AD051</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>saniyaue5@gmail.com</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Anix Saju</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>JEC23AD014</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Naseef Rahman Ashraf</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>JEC23AD043</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Ayisha Tooba KM</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>JEC23AD022</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46250.52352394676</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>saniyaashraf.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Mini Project</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI-Based Ayurvedic Medicinal Plant Identification and Usage Information System</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accurate identification of Ayurvedic medicinal plants and understanding their safe usage remains a challenge for non-experts due to the complexity and diversity of plant species. This project proposes an AI-based Ayurvedic Plant Identification and Usage Information System that combines deep learning image classification with a structured medicinal knowledge base. The system accepts an image of a plant and uses a convolutional neural network (CNN) trained on medicinal plant datasets to classify the species. Upon identification, detailed information is retrieved from the knowledge base, including the plant’s scientific and common name, medicinal properties, therapeutic uses, usable parts, toxicity concerns, and preparation methods. By integrating image-based plant identification and contextual Ayurvedic knowledge, the system offers a user-friendly and reliable platform that enhances access to traditional plant wisdom while promoting safe and informed utilization of medicinal plants. This approach is supported by recent research demonstrating the effectiveness of deep learning models in medicinal plant recognition and classification, as well as structured methods for linking classification results to domain-specific information. The system can be extended to include additional species and expanded informational content in future work.  </t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>AI, Deep Learning, CNN, MobileNetV2, TensorFlow, Python, Flask, Computer Vision</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1fNYjKYjpwyLJjCD05RhXz_2W3Dz3zZgh</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1Elm3V7OTmmiUGnX8xQuomNopFRZbp_27</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Anjali O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Saniya Ashraf</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>JEC23AD051</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>saniyaue5@gmail.com</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Anix Saju</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>JEC23AD014</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Naseef Rahman Ashraf</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>JEC23AD043</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Ayisha Tooba KM</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>JEC23AD022</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46250.564005625</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>pavandass.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Pipeline Hazard Detection and Resolution Using RISC-V (Ripes Simulator)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This project focuses on the **detection and resolution of pipeline hazards in a RISC-V processor** using the **Ripes simulator**. Pipelining improves processor performance by allowing multiple instructions to be processed simultaneously through different stages. However, overlapping instruction execution can introduce hazards that may affect the correctness and efficiency of the processor.
+The project demonstrates a **five-stage RISC-V pipeline consisting of Instruction Fetch (IF), Instruction Decode (ID), Execute (EX), Memory Access (MEM), and Write Back (WB)** stages. Three major pipeline hazard scenarios are implemented using RISC-V assembly programs and analyzed through the simulator. **Data hazards** are demonstrated using dependent arithmetic instructions and resolved through **data forwarding**, allowing results to be passed directly to the required pipeline stage without unnecessary stalls. **Load-use hazards** are demonstrated using a load instruction followed immediately by a dependent instruction. Since the loaded data is not available soon enough, the **Hazard Detection Unit (HDU)** introduces a one-cycle stall or bubble before execution continues. **Control hazards** are demonstrated using branch instructions, where instructions fetched from the wrong execution path are removed through **pipeline flushing** when the branch is taken.
+The project uses Ripes to visualize instruction movement across pipeline stages and observe forwarding paths, stalls, and flushed instructions. The simulation results demonstrate how different hazard-resolution techniques maintain correct instruction execution while minimizing performance penalties. This provides a practical understanding of pipeline operation, hazard detection, and hardware-level resolution techniques in modern processor architectures.
+</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>RISC-V, Ripes Simulator, Assembly Language, Processor Pipelining, Pipeline Hazard Detection, Data Forwarding, Hazard Detection Unit (HDU), Pipeline Stalling, Pipeline Flushing</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1fpbpp1LW3eJocpGQMjUaw_YR0O9fSNit</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1WTJ9CToloH99cgAGUJ_IRlo2rr650lJb</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>SAJITHA SIVAN</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>PAVANDAS S</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>JEC24AD070</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>pavanarikkinchira@gmail.com</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>JONES MALIYAKEL ABRAHAM</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>JEC24AD049</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>KEERTHANA B</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>JEC24AD053</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>SANA FATHIMA P B</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>JEC24AD076</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46250.59022601852</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>jovitjoshy.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Student Attendance Management System </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>The Student Attendance Management System is a database management system designed to efficiently record, manage, and monitor student attendance in an educational institution. Maintaining attendance records manually can be time-consuming and may lead to errors, duplication, or difficulty in retrieving information. This project provides a computerized solution that stores attendance-related information in a structured database.
+The system maintains details of students, faculty members, subjects, and daily attendance records. Faculty members can record the attendance of students for different subjects and dates. The system allows users to add, update, delete, and retrieve student and attendance information easily. It can also calculate the attendance percentage of individual students based on their attendance records.
+The proposed system uses a relational database to establish relationships between students, subjects, faculty, and attendance records. SQL queries can be used to perform operations such as searching for student details, viewing subject-wise attendance, identifying students with low attendance, and generating attendance reports.
+The main objective of this project is to reduce manual work, improve the accuracy of attendance records, and provide quick access to attendance information. The system also demonstrates important DBMS concepts such as tables, primary keys, foreign keys, relationships, normalization, SQL queries, and data manipulation.
+Overall, the Student Attendance Management System provides a simple, reliable, and organized method for managing student attendance. It can be further enhanced with features such as login authentication, automated notifications for low attendance, graphical reports, and web or mobile-based access.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>MySQL, SQL, HTML, CSS, PHP</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=17QB7yacS7oFet0e8vt-UJWIsHJlDUuxH</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1Tw7aJwY8pq0M6t1dGfw62hcBkJylUM8e</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Jovit Joshy</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>JEC24AD052</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>jovitjoshy.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Safwan C Salam</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>JEC24AD094</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Vysakh Praveen</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>JEC24AD092</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Adharsh Krishna P M</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>JEC24AD093</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>46250.62117197917</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>shaunsajie.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Genetic Disease Risk Classifier</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>The Genetic Disease Risk Classifier is a machine learning-based healthcare project designed to classify the risk of genetic diseases by analyzing relevant genomic, clinical, and demographic features. The system aims to demonstrate how artificial intelligence can be applied to healthcare data to support early identification and classification of genetic disease patterns.
+The project uses a dataset containing samples associated with five genetic diseases: Thalassemia, Hemophilia, Breast Cancer, Sickle Cell Anemia, and Cystic Fibrosis. The machine learning workflow includes data preprocessing, cleaning, feature transformation, scaling, model training, evaluation, and visualization. Multiple classification algorithms, including Logistic Regression and Random Forest Classifier, are implemented and evaluated using metrics such as accuracy, confusion matrix, classification report, ROC curve, and AUC score.
+To improve model transparency, the project incorporates Explainable AI (XAI) using SHAP (SHapley Additive Explanations). This helps identify the most influential features and understand how individual features contribute to the model's predictions. This interpretability is particularly important in healthcare applications, where understanding the reasoning behind a prediction is valuable.
+An interactive Gradio-based prediction interface is also developed, allowing users to enter relevant parameters and receive real-time disease classification results. The project is implemented using Python, Pandas, NumPy, Scikit-learn, Matplotlib, Seaborn, SHAP, Gradio, and Joblib, with the model development and experimentation performed through a Jupyter/Google Colab workflow.
+Overall, the project demonstrates an end-to-end application of machine learning, data preprocessing, model evaluation, explainable AI, and interactive deployment for genetic disease classification. It serves as an academic prototype for exploring AI-assisted healthcare analytics and can be further enhanced through larger datasets, additional diseases, advanced deep-learning techniques, and cloud-based deployment.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Python, Machine Learning, Random Forest, Scikit-learn, SHAP, Gradio</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1gyg2t5rSrF61hv68NbIfCxyvYZILt6v2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1xH1J61-T_lhdFWiIIeR-Q4QsEQt-S2B8</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Shaun Saji E</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>JEC24AD080</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>shaunsajie2@gmail.com,(https://github.com/Shaunsajie/Genetic-Disease-Risk-Classifier)</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> KEERTHANA B</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>JEC24AD053</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> SREELAKSHMI AJITHAN</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>JEC24AD084</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>VYSAKH PRAVEEN</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC24AD092 </t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>46250.62724943287</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>shaunsajie.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Password / PIN Verification System (Ripes)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>The Password/PIN Verification System is a computer architecture project that implements a basic authentication mechanism using RISC-V Assembly Language and the Ripes processor simulator. The project demonstrates how fundamental processor instructions and control-flow operations can be used to implement a practical security-oriented application at the assembly level.
+The system stores a predefined PIN in memory and compares it with the user-entered PIN, which is simulated through memory. The verification process uses RISC-V instructions, particularly comparison and branching operations such as beq, to determine whether the entered credentials match the stored PIN. If the PIN is correct, the system grants access; otherwise, the attempt counter is reduced and the user is allowed to try again.
+A key feature of the project is its three-attempt authentication mechanism. After three consecutive incorrect attempts, the system automatically blocks access, demonstrating a simple protection mechanism against repeated unauthorized login attempts. The project also makes use of loops, conditional branching, memory operations, and register-based processing to demonstrate how a real-world authentication workflow can be translated into low-level processor instructions.
+The entire execution is simulated and visualized using Ripes, allowing the instruction flow and processor operations to be observed at the architectural level. This provides a practical understanding of RISC-V RV32I architecture, assembly programming, instruction execution, memory access, branching, and processor control flow.
+Overall, the project connects computer architecture concepts with a real-world authentication application. It demonstrates how basic processor-level operations such as loading data, comparing values, branching, looping, and updating counters can be combined to create a functional PIN verification system. Future improvements could include real-time user input, password encryption, and implementation on physical hardware such as an FPGA.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>RISC-V, Assembly Language, Ripes Simulator, Computer Architecture</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1fn1rpsKqtnEBimvhI2NYpX4zCW_uZoYj</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1kYmgLLzvngGgX1wsIYQ6Ih9x3yWBplIh</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Sajitha A S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Shaun Saji E</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>JEC24AD080</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>shaunsajie2@gmail.com, https://github.com/Shaunsajie/coa-pin-verification-ripes</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Maria Ann Mathew</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>JEC24AD060</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Vysakh Praveen</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>JEC24AD091</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Niranjana P P</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>JEC24AD066</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>46250.66428434028</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>mariaannmathew.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Blood Bank Management Project</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>A Blood Bank Management System is a software system that:
+Stores blood availability data
+Manages donor and blood stock information
+Helps hospitals and patients request blood easily
+It replaces manual registers and phone calls.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1R25FIfjUtxIcJkWSo-5G-dGnQ0iG3C6L</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1vTg5NsFNprEIS-3KhCgoyIxXAbdtyZqb</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maria Ann Mathew </t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC24AD060 </t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Mariaannmathew654@gmail.com , https://github.com/MariaAnn1/BloodBankProject</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Niranjana pp</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>JEC24AD066</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Paul Dix</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>JEC24AD069</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oshly Jobko </t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>JEC24AD0668</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>46250.66858068287</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>sreelakshmimp7228@gmail.com</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Cache Memory Performance Analysis Tool Using Ripes Simulator</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Cache memory plays a vital role in improving the performance of modern processors by reducing memory access time. This project presents a Cache Memory Performance Analysis Tool implemented using the Ripes simulator. The objective of this project is to study the effect of cache parameters such as cache size and cache organization on processor performance. By executing the same RISC‑V program under different cache configurations, parameters such as cache hits, cache misses, execution cycles, and CPI are observed and analyzed. The results demonstrate that increasing cache size and associativity significantly reduces cache misses and improves overall system performance. This project helps in understanding the importance of cache memory in computer architecture.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>RISC-V, Cache Memory, Computer Architecture, Ripes Simulator</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1xyz03wSEKA_AK0dduo2iR4R-Du-DFh0w</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=19QznPFWNQ1PMtxABVNhfOCuVAbMdSzql</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sajitha A S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>VRINDHA MANOJ KUMAR</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>JEC24AD091</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>vrindhamanojkumar.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>SREELAKSHMI MP</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>JEC24AD085</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>NANDHITHA MADHAVAN C M</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>LJEC24AD095</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>ADHARSH KRISHNA P M</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>LJEC24AD093</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>46250.66898457176</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>aishwaryadineshrao.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Main Project</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Motor Imagery EEG Classification for BCI-Controlled Home Automation</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physically challenged individuals with severe motor impairment often cannot operate conventional switches or remote controls, leaving them dependent on caregivers for basic tasks such as turning on a light or a fan. This project designs and simulates an EEG-based Brain–Computer Interface (BCI) home automation system that lets a user control household appliances using imagined movement rather than physical action. Because collecting large volumes of subject-specific EEG data is impractical within a single project phase, the system is developed and validated using the publicly available BCI Competition IV 2a (BCICIV 2a) Motor Imagery dataset, which is replayed to simulate a live EEG stream. Recorded signals are band-pass filtered and artifact-corrected, then classified by a deep learning model into one of four motor imagery classes — left-hand, right-hand, foot, and tongue movement. Each recognised class is mapped to a specific appliance command and sent to an ESP32 microcontroller, which actuates a 4-channel relay module to switch the corresponding appliance. A companion mobile/web dashboard displays the simulated EEG stream, the currently detected command, live appliance status, and a historical activity log. </t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>EEG, BCI, Deep Learning, CNN, Signal Processing, Motor Imagery, ESP32, IoT, Relay Module, Web Dashboard</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1s2TOdxgfrCzY3TYNXhbf09AP1Kfl5mnc</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1xYq7XWlm0E0QIjAlCqqtfXAZN9l_Yqkx</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Anoop V</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Aishwarya Dinesh Rao</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>JEC23AD005</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>aishwaryadineshrao.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Abirami S</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>JEC23AD003</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Alet Jose</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>JEC23AD009</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Aneesh V</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>JEC23AD012</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>46250.67661908565</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>bilalv.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>YouTube Trending Video  Recommender System</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>YouTube Trend Analysis is a data-driven project that develops a YouTube Trending Video Recommender System to identify and recommend popular videos based on user-provided keywords. The project analyzes YouTube trending video data using data science and machine learning techniques to understand audience engagement and content popularity. Ten publicly available YouTube trending datasets were combined, initially containing 375,942 records and 16 features. The data was preprocessed by removing irrelevant columns, checking data quality, handling typing errors, removing duplicate records, converting categorical features into numerical form using Label Encoding, detecting outliers using the Interquartile Range (IQR) method, and applying Min–Max normalization. Exploratory Data Analysis was performed using bar charts and boxplots to study relationships between views, likes, comments, and video popularity. A Random Forest model was used for predicting whether videos belong to the trending category. The processed features included views, likes, channel normalization, and category ID. The dataset was divided into training and testing sets, with 80% used for training and 20% for testing. The system also provides a user interface developed using Gradio, where users can enter a keyword and obtain a recommended trending video along with relevant details and a YouTube link. The project demonstrates how data analytics and machine learning can be applied to understand digital content trends and assist viewers, content creators, marketers, and researchers in discovering popular content.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Python, Pandas, Scikit-learn, Random Forest, Machine Learning, Data Science, Matplotlib, Gradio</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1Yhh-F92n6SXMHiVvZMgogcugWu2bbvS7</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1B0b27SvMbveau9onQ1Da2ocT7NgOwCAq</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Divya Konikkara</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JESNA C J </t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC24AD046 </t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>jesna-design</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>ADHISREE P A</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC24AD006 </t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BILAL V </t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC24AD033 </t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>46250.68892686343</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>devikaswarup.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Array Summation using RISC-V architecture </t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Array Summation Using RISC-V Architecture is a micro project that demonstrates the implementation of array summation using RISC-V assembly language and the Ripes simulator. The project focuses on understanding how a processor accesses data from memory, performs arithmetic operations, and controls program execution through loops and branch instructions.
+In the implementation, array elements are stored sequentially in memory and accessed using load instructions. Each element is added to an accumulator register until all elements have been processed. This demonstrates fundamental concepts of memory access, register operations, arithmetic computation, and loop-based instruction execution. 
+The Ripes simulator provides a visual environment for observing registers, memory, datapath, and processor pipeline stages during program execution. This enables practical understanding of how instructions are fetched, decoded, executed, and written back within a processor. 
+Overall, the project provides hands-on exposure to RISC-V architecture, assembly language programming, memory addressing, register manipulation, and processor instruction execution, helping bridge the gap between theoretical computer architecture concepts and their practical implementation.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>RISC-V, RISC-V Assembly, Ripes Simulator, Processor Simulation</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1UX5_H9bOYYs_vzqyhKFvY6c-XXBeQsOY</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1IvISb3S0TgvdBMsl8s2EV64BMgo52BMz</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sandeep C S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Devika Swarup </t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>JEC24AD037</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>devikaswarup</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aivin Varghese </t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>JEC24AD008</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Akshay A</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>JEC24AD010</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Anu V Nair</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>JEC24AD021</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>46250.72073646991</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>vrindhamanojkumar.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI-Driven Intelligent Library Database Management System Using MySQL  for Automated and Predictive Library Services</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>This paper describes the design and development of an AI-Integrated Library Database Management System (AI-DBMS), a 
+system that pairs a relational database backend with artificial intelligence techniques to automate and intelligently upgrade the 
+day-to-day running of a college library. Conventional library setups still rely heavily on manual record-keeping, which leads 
+to duplicated data, slow processing, and a frustrating experience for users. To address this, the proposed system pairs a MySQL 
+database with a Python-driven AI layer that provides book recommendations, automatic fine calculation through SQL triggers, 
+natural-language search, and inventory forecasting. A four-tier architecture links a Tkinter-based interface to an AI-enhanced 
+application layer, which in turn sits on top of a fully normalised relational schema. Referential integrity and data consistency 
+are maintained through SQL constructs such as foreign keys, triggers, stored procedures, and views. On the AI side, the system 
+uses collaborative filtering to personalise recommendations, a rule-based chatbot to answer member queries, and a regression-
+based module to forecast demand. Testing on a simulated dataset of 500 books, 200 members, and 1,200 transactions shows 
+clear gains in issuance speed, data accuracy, fine consistency, and user engagement over both manual record-keeping and 
+conventional library software that lacks AI features, with overall satisfaction rising from 5.2 to 8.9 on a 10-point scale</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>AI, DBMS,TKINTER ,PYTHON,SQL</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1rP0i5zLen2Vi8vrPvxVSiyNTKMPLiSk1</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1mNAw_hy67weDqrMEZjZC4_JL7-LBbZ_3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vrindha manoj kumar </t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>JEC24AD091</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>vrindha.mnj@gmail.com</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sreelakshmi mp </t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>JEC24AD085</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Keerthana krishna </t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>JEC24AD054</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sreelakshmi ajithan </t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>JEC24AD084</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>46250.72764769676</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>raveenavr.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Mini Project</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Real-Time Bharatanatyam Transcription Using MediaPipe Holistic, Geometric Heuristics, and Adaptive KNN Classification</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bharatanatyam is an extremely codified classical Indian dance form where intricate hand gestures called Mudras, facial expressions called Navarasas, and body postures are utilized to perform complex storylines. The traditional method for transcribing this highly dynamic and interrelated movement is an extremely labor-intensive and resource-intensive task that demands significant domain knowledge. We propose an advanced real-time transcription system called Natyam Transcribe based on web technology for automatic transcription and semantic interpretation of Bharatanatyam performances using complex hand gestures, facial expressions, and body postures. Our proposed system utilizes a combination of Google’s MediaPipe Holistic framework for extracting 3D skeletal landmarks and an innovative mathematical heuristic-based inference engine based on the rules of Abhinaya Darpanam for accurate classification of complex hand gestures, facial expressions, and body postures. Our proposed system can accurately classify the 28 primary Asamyukta Hastas, 9 primary Navarasa expressions, and body postures in real-time. Moreover, an instance-based KNearest Neighbors classifier, called the ”Teach AI” feature, is incorporated for dynamically training the classifier for customized or unseen choreographed hand gestures. Our proposed system can achieve an accuracy rate of 92% with an inference rate of over 20 frames per second and Samyukta Hastas detection latency of less than 50 ms, thus proving the viability of our proposed system for digital preservation of classical Indian dances.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Python, MediaPipe Holistic, OpenCV, Machine Learning, KNN, Deep Learning, Computer Vision</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1XmuNzub9o9KIVwSzdnP2wadMNb3T_igU</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1TBC3saXFg05Q9pVZseJJp0HjJcDzkmPE</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Arjun K M</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Raveena V R</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>JEC23AD048</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>raveenarajeevan00@gmail.com</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Keerthy K</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>JEC23AD033</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Prabin V P</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>JEC23AD047</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Sania Rajesh</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>JEC23AD050</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>46250.7458494213</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>annmariyathomas.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Swapping two numbers</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>This micro project demonstrates the swapping of two numbers stored in processor registers using RISC-V assembly language and the Ripes RISC-V simulator. The project focuses on understanding how low-level instructions interact with processor registers and how data is transferred during instruction execution.
+In the implementation, two values are initialized in RISC-V registers x1 and x2. A temporary register x3 is used to store one value while the other value is transferred between the registers, thereby successfully exchanging the two numbers. The program is executed and analyzed using the Ripes simulator, which provides a graphical visualization of processor components such as the program counter, instruction memory, register file, ALU, data path, and pipeline stages.
+The project also examines the five-stage RISC-V pipeline consisting of Instruction Fetch, Instruction Decode, Execute, Memory Access, and Write Back. The step-by-step execution in Ripes enables observation of instruction flow, register-value changes, and processor behavior during the swapping operation. Execution metrics and the register values before and after execution are analyzed to verify the correctness of the implementation.
+The project provides practical exposure to RISC-V architecture, assembly language programming, register operations, instruction execution, and processor data path visualization. It demonstrates how a simple data manipulation operation can be used to understand fundamental concepts of Computer Organization and Architecture and helps bridge the gap between theoretical concepts and actual processor execution.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>RISC-V, Assembly Language, Ripes Simulator, Computer Organization and Architecture</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1CwAgLEELuqqf9DKB9Y_EUtw_iJz1CvAJ</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=18am4BdiG0DheDsLv_6FTK8qFGtzzLqGV</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sandeep C S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ANN  MARIYA THOMAS</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>JEC24AD019</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://github.com/crazyvellara</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARJUN SREENIVAS P	</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>JEC24AD022</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADARSH P K        </t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>JEC24AD005</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AYSHA  FEMIN </t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>JEC24AD029</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>46250.74951101852</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>aljona.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>BLINKING OF LED IN RGB PATTERN USING  RIPES</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This micro project focuses on simulating the blinking of an RGB LED using the RISC-V architecture in the RIPES simulator. The main objective is to demonstrate how low-level assembly language instructions can control an output device through memory-mapped I/O. The project uses a virtual RISC-V processor environment to establish communication between the CPU and a simulated RGB LED. The assembly program sequentially sends values corresponding to red, green, and blue colors to the LED and uses software-based delay loops to maintain each color for a visible duration. The sequence is continuously repeated to create the RGB blinking effect. The project also provides practical exposure to RISC-V instruction execution, registers, processor datapath, pipelining, and input/output operations. The RIPES simulator allows the execution process, register changes, pipeline stages, and LED output to be observed visually. The project successfully demonstrates the interaction between software instructions and hardware-like output components without requiring physical hardware. It helps bridge the gap between theoretical concepts of Computer Organization and Architecture and their practical implementation. </t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>RISC-V, Assembly Language, Computer Organization and Architecture, RIPES Simulator, Memory-Mapped I/O, Processor Pipelining</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1YVSGmHfnnMZZSJ8suqoxKnpT7l-pZb3A</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1du7dnkRrl6rhQV1pQglXkbOitmKeIIYq</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sandeep C S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>JESNA C J</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>JEC24AD046</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>jesna-design</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>ALJO  N A</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>JEC24AD012</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>ANUSREE K</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>JEC24AD020</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>46250.76094974537</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>annmariyathomas.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ELECTRICITY USAGE ANALYSIS IN A HOUSEHOLD</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Electricity Usage Analysis in a Household is a data science and machine learning project developed to analyze household electricity consumption and predict electricity bills based on appliance usage, monthly operating hours, and tariff rates. The project addresses the difficulty faced by households in estimating monthly electricity costs due to varying appliance usage patterns and electricity tariffs.
+The project uses a structured electricity usage dataset containing numerical features such as Fan, Refrigerator, Air Conditioner, Television, Monitor, Monthly Hours, Tariff Rate, and Electricity Bill. The dataset was obtained from an open-source Kaggle repository and stored in CSV format. Data preprocessing was performed using Python, including data loading, schema validation, missing-value checking, duplicate detection, data transformation, and outlier analysis. Exploratory Data Analysis was carried out using statistical analysis, boxplots, histograms, correlation matrices, and heatmaps to understand the relationships between appliance usage and electricity costs.
+Since the target variable, Electricity Bill, is a continuous numerical value, a supervised regression approach was selected. Multiple Linear Regression was implemented to establish the relationship between the independent variables and the electricity bill. Model performance was evaluated using Root Mean Squared Error (RMSE) and the coefficient of determination (R²). The analysis identified Monthly Hours, Tariff Rate, and Air Conditioner usage as important factors influencing electricity costs.
+The developed model was also used to predict the electricity bill for new household input values. The project demonstrates how data science and machine learning can be applied to a practical household energy-management problem. It provides an interpretable approach for estimating electricity costs, increasing energy awareness, supporting cost optimization, and encouraging more sustainable electricity consumption.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Python, Pandas, NumPy, Matplotlib, Seaborn, Multiple Linear Regression</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=14_tN8wuL96hJDWVnKLHaAz_XzokDSFks</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1o6NEDdZ7eqD761g2riSvWgyWp2hfbNlx</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Divya Konikkara</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ANN MARIYA THOMAS</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>JEC24AD019</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>crazyvellara</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>ARJUN SREENIVAS P</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>JEC24AD022</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>AYSHA FEMIN</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>JEC24AD029</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> AIVIN VARGHESE  </t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> JEC24AD008</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>46250.779465625</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ayshashazakaniyatta.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Prediction of Malnutrition in Children</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Project Abstract / Brief Description
+This project focuses on the prediction and analysis of malnutrition in children and its associated health risks using data science and machine learning techniques. The study analyzes global malnutrition trends using key indicators such as stunting, wasting, and underweight prevalence among children across different countries.
+The project involves collecting and preprocessing malnutrition-related data by removing unnecessary columns, checking for missing values, selecting the latest available year for each country, and ensuring that numerical values are represented appropriately. Exploratory Data Analysis (EDA) was then performed using histograms, boxplots, correlation analysis, and comparisons across income groups to identify patterns, inequalities, and countries with unusually high malnutrition levels.
+The analysis identified countries with high prevalence of underweight, stunting, and wasting. Strong correlations were also observed between the malnutrition indicators, particularly between underweight and stunting (0.84) and underweight and wasting (0.82). The project also examined the relationship between income level and malnutrition, showing greater variation and higher prevalence among lower-income countries.
+For prediction and classification, underweight prevalence was selected as the target indicator, with values above 20% considered indicative of high malnutrition. A Random Forest Classifier was trained to classify countries into high- and low-malnutrition categories. The model achieved an accuracy of 96% based on the evaluation results.
+The project provides a data-driven approach to identifying countries at higher risk of malnutrition and can support early identification of areas requiring greater nutritional and healthcare attention. The findings also contribute to the objectives of SDG 1 (Zero Hunger) and SDG 2 (Good Health and Well-being) by supporting the identification of malnutrition risks and promoting timely preventive action.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Datascience/Artificial intelligence/ Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1VSwfV_9zKg36Ry0uL2iB_b_qYLTg8oQI</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1wc882Orn7DQ98Yfuu3xdmomSy81GPwb9</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Divya Konikkara</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Aysha Shaza Kaniyatta</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>JEC24AD031</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>aysha.shaza3939@gmail.com</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Anjana P A</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>JEC24AD017</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Anusree K</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>JEC24AD020</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>46250.80678217593</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>akhilbijuthudumel.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2025-29 (S3)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Lung cancer prediction</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>The main objective of this project is to develop a machine learning-based predictive system
+that can accurately identify individuals at risk of lung cancer using patient data. The system
+uses the Random Forest Classifier to perform binary classification (Cancer / No Cancer) based on health-related attributes.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Numpy, Pandas, machine learning, Gradio</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1qtO_TvVPyq064vTQm0GHafEup6KuS_EP</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1YZo2F2_NJrzaTw5rAz756Yndu-rGomfW</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Divya Konikkara</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>AKHIL BIJU THUDUMEL</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>JEC24AD009</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>akhil80610</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>AADITI SANDEEP</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>JEC24AD001</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>ADARSH PK</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>JEC24AD005</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>DEVIKA SWARUP</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>JEC24AD037</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>46250.81786780093</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>sreyasmechinath.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Intelligent crop recommendation system</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Intelligent Crop Recommendation System
+The Intelligent Crop Recommendation System is a machine learning-based application designed to help farmers select the most suitable crop for cultivation based on environmental and soil conditions. The system analyzes important agricultural parameters such as soil nutrients (N, P, K), temperature, humidity, rainfall, and soil pH to recommend a crop that is likely to grow successfully under the given conditions.
+The proposed system uses a trained machine learning model to identify relationships between these factors and suitable crops. By providing the required soil and climatic parameters, users can obtain a crop recommendation quickly and efficiently. This can reduce dependency on guesswork and support better agricultural decision-making.
+The system aims to improve crop productivity, promote efficient use of resources, and reduce the risk of selecting unsuitable crops. It can be developed as a user-friendly web application where farmers or agricultural users enter the available field conditions and receive the recommended crop as the output. The project demonstrates the practical application of **machine learning, data analysis, and agricultural technology** to address real-world farming challenges.
+Overall, the Intelligent Crop Recommendation System provides a simple and intelligent approach to data-driven crop selection and can contribute to more efficient and sustainable agricultural practices.
+</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Python,Machine Learning,MySQL,Pandas</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1OjSD4ih1zCz99u9M1r_fttIR4a00URb8</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1qlZVr8IrsYop-HU4YzleHPShiFT3WP4i</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sajitha A S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Sreyas Mechinath</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>JEC24AD088</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>srzzsjayy</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>KP Adithya Dev</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>JEC24AD056</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Krishnakumar ER</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>JEC24AD057</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Niranjana PP</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>JEC24AD066</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>46250.83139243055</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ayshashafeek.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Performance Analysis of Arithmetic Operations Using RISC-V simulator</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABSTRACT
+In the field of **Computer Organization and Computer Architecture, understanding how a processor executes instructions is fundamental to analyzing system performance and efficiency. Modern computing systems rely heavily on optimized instruction execution techniques to achieve high performance. Among various types of instructions, arithmetic operations such as addition, subtraction, multiplication, and division form the core of almost every computational task. These operations are extensively used in applications ranging from basic calculations to complex scientific simulations, data analysis, and real-time systems. Therefore, studying the behavior and performance of arithmetic instructions within a processor becomes essential for gaining deeper insights into system design.
+This project focuses on the analysis and simulation of arithmetic instruction execution using the RIPES simulator, based on the RISC-V architecture. RISC-V is a modern, open-standard Instruction Set Architecture (ISA) that follows the principles of Reduced Instruction Set Computing (RISC). Its simplicity, modularity, and flexibility make it highly suitable for educational purposes, research, and processor design. Unlike traditional proprietary architectures, RISC-V allows users to study and modify its design, thereby providing a deeper understanding of how processors function at a low level.
+The RIPES simulator provides a graphical and interactive environment that enables users to visualize the internal operations of a processor. It allows step-by-step execution of instructions, making it easier to observe how data flows through different components such as registers, the Arithmetic Logic Unit (ALU), and memory. One of the key features of RIPES is its ability to demonstrate the working of a pipelined processor, where multiple instructions are executed simultaneously at different stages. This visualization helps in understanding the concept of instruction-level parallelism and how it contributes to improved performance.
+Through this project, arithmetic instructions are implemented using RISC-V assembly language and executed within the RIPES simulator. The behavior of each instruction is carefully observed, including how registers are updated and how results are generated. The project also examines how instructions move through different pipeline stages and how hazards such as data hazards and control hazards influence execution. By analyzing these factors, the project provides a comprehensive understanding of processor performance at a micro-level.
+The results obtained from the simulation highlight the efficiency of pipelined execution and demonstrate how arithmetic operations are processed within a RISC-V processor. The project also emphasizes the importance of simulation tools in bridging the gap between theoretical concepts and practical understanding. By visualizing internal processor operations, students can better grasp complex topics that are otherwise difficult to understand through theory alone.
+In conclusion, this project serves as a valuable learning experience in understanding processor architecture, instruction execution, and performance optimization techniques. It not only enhances theoretical knowledge but also provides practical exposure to simulation-based analysis, thereby preparing students for advanced studies and research in computer architecture and related fields.
+</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Computer Architecture / Embedded Systems / Computer Organization</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1BBITmWQtZBDZR_oRRqS5-wlNW6drDqeY</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1SHLk7pbH8YV2JsYxuV6_5TQSuL1urVgQ</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sandeep C S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>AYSHA SHAFEEK</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>JEC24AD030</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>ayshashafeek205@gmail.com</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>AYSHA SHAZA KANIYATTA</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>JEC24AD031</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AYSHA ABDUL HAQUE </t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>JEC24AD028</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>BASIL K DAVID</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>JEC24AD032</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>46250.84413961806</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>anandgk.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Urban Water Consumption Prediction and Forecasting System using Machine Learning</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Rapid urbanization, climate variability, and population growth place immense pressure on municipal water supply systems. Accurate forecasting of water demand is critical for sustainable resource allocation, infrastructure planning, and drought mitigation. This project presents an end-to-end Machine Learning system designed to predict urban water consumption (in megalitres) at the ward level.
+The dataset incorporates demographic, climatic, and infrastructure metrics—including population, average household size, median income, temperature, rainfall, reported leakages, and water supply. Data preprocessing handles ward-level missing values via median/mean imputation, applies IQR capping for extreme outliers, and performs cyclic encoding (sine/cosine transformations) on temporal features to capture seasonal demand fluctuations.
+Supervised regression algorithms—specifically Random Forest Regressor and Gradient Boosting Regressor—are trained and evaluated using metrics such as RMSE, MAE, and R^2. The optimal model is serialized and deployed via a high-performance FastAPI backend, integrated with an intuitive, responsive web frontend. The web application allows urban planners and municipal authorities to input demographic and weather forecasts and receive instantaneous, ward-specific consumption estimates.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Machine Learning, Python, FastAPI, Scikit-learn, Pandas, HTML/CSS/JavaScript</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1TrPsjNejDq0OSdO2tq_QC4Llr_yg0ScU</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1Qc6nvyuug61NBOujoNa52IraHiyT1pbY</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Divya Konikkara</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>AKSHAY A</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>JEC24AD010</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>akshaya.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>ANAND G K</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>JEC24AD015</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>ARYA K A</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>JEC24AD023</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>FATHIMA MISNA T E</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>JEC24AD041</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>46250.85646028935</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>bhuvanyavs.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Mini Project</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AI POWERED PERSONALISED STUDY SCHEDULING SYSTEM</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>This project focuses on developing an AI-powered Personalized Study Scheduling System that helps students plan and manage their studies efficiently. It generates customized study plans based on goals, subjects, availability, and performance, while using adaptive scheduling, progress tracking, and smart reminders to improve consistency and academic performance.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>AI, Machine Learning, Adaptive Scheduling, Recommendation Systems, Python, Flask, SQL</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1OFiqUvHLAYqwRaA7Wek42IvKwFj5zIkX</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1THC0UZvtjwPE39wWyy8C3kr7hKPs99El</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Mrs. Reni Jose</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Aquamol Tony</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>JEC23AD017</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>aquamoltony@gmail.com</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Bhuvanya VS</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>JEC23AD025</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Fatima Alzahra</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>JEC23AD027</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Nived Krishna P</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>JEC23AD044</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>46250.86302483796</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>asnaa.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Function Call Overhead Analysis</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Function Call Overhead Analysis focuses on analyzing the execution overhead introduced by function calls using the RISC-V instruction set architecture. Function calls support modular and reusable programming, but they require additional instructions for control transfer, return-address handling, parameter passing, and returning to the calling program. This project demonstrates how function calls are implemented at the processor level using RISC-V assembly language. Instructions such as Jump and Link (JAL) and Jump Register (JR) are used to transfer control between the main program and functions while managing return addresses. The implementation is performed using the RIPES simulator, which provides a graphical representation of registers, memory, and pipeline stages. Step-by-step execution allows the behavior of instructions and data flow during function calls to be observed clearly. The project analyzes the additional computational steps associated with function calls and their effect on processor performance. It also demonstrates the trade-off between execution efficiency and the modularity, readability, and maintainability provided by functions.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>RISC-V, Assembly Language, RIPES Simulator, Computer Architecture, Processor Pipelining</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1vYkat9qDgnZ47pm-h-SBZaAIVumqbcd4</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1UH9OFvV1QQUwlOSZWJ0WYmoDEGvEBtlL</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Sandeep C S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Asna A</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>JEC24AD025</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>asnusabi@gmail.com</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Cherian Aby Elenjikkal</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>JEC24AD034</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Derek Johny M</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>JEC24AD035</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Hadiya M</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>JEC24AD043</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>46250.88758171297</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>amankr.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Mini Project</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forecasting Medicine Stock-Out Risk Using Historical Sales Data </t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Medicine stock-outs can create serious problems in healthcare, particularly in rural clinics where timely availability of essential medicines is important. This project develops a machine learning-based system to forecast the possibility of medicine stock-outs using historical medicine sales data. The dataset contains daily sales information for multiple medicine categories along with time-related attributes such as year, month, hour and weekday.
+The project begins with data preprocessing, including checking and handling missing values, removing duplicate records, converting date information into the appropriate format, and preparing the dataset for machine learning. Historical sales patterns are then used to identify instances where medicine sales reach zero, which are treated as potential stock-out events for this project.
+A separate Random Forest classification model is trained for each medicine category. The models learn patterns from historical data and use time-related features to classify whether a medicine is likely to experience a stock-out. The trained models are evaluated using test data and are then used to generate stock-out predictions for the following seven days.
+The final system presents the prediction results in an understandable format and exports the seven-day forecasts for each medicine to an Excel file. The proposed approach demonstrates how data science and machine learning can support proactive medicine supply planning and help healthcare facilities identify potential shortages earlier.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Data Science, Machine Learning, Python, Pandas, Scikit-learn</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=17lE_HsLcC677or7fE9_9wgADN0-Ca6Yl</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=12Bwmis4QnYb0SHqU9HB7rwr3ogE_WNxq</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Divya Konikkara</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>AMAN K R</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>JEC24AD013</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>amanramesh1@gmail.com</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>ALAN E ALEXANDER</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>JEC24AD011</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>HADIYA M</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>JEC24AD043</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>ASHLIN THERES JAMES</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>JEC24AD024</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>46250.88928549769</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>muhammedshammasca.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Cardio Doctor Assistant</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Cardio Doctor Assistant is a web-based machine learning application designed to provide preliminary cardiovascular risk assessment and assist patients before consulting a doctor. The system collects basic health information and symptom-related responses through a simple and user-friendly questionnaire. Patients can provide details such as age, blood pressure, cholesterol level, smoking habits, diabetes status, exercise habits, and the severity of selected symptoms.
+The collected data is processed using Python, Pandas, NumPy, and Scikit-learn. A machine learning classification model, such as a Random Forest Classifier, is trained using a cardiovascular health dataset to analyze the patient's inputs and classify the possible risk level into categories such as Low, Medium, High, or Very High.
+After analyzing the responses, the system displays the predicted risk level and provides preliminary suggestions about appropriate medical tests, such as ECG, blood tests, stress tests, or echocardiography, depending on the risk category. The system is intended to support early awareness and help patients understand when professional medical consultation may be appropriate. It is not intended to replace a qualified doctor or provide a medical diagnosis.
+The application uses Flask as the backend framework and HTML, CSS, and JavaScript for the web interface. The trained machine learning model is stored and integrated with the Flask application so that new patient responses can be analyzed in real time.
+The main objective of this project is to demonstrate how machine learning, data analysis, and web technologies can be combined to develop a healthcare assistance system. Future improvements may include larger and clinically validated datasets, more detailed symptom severity analysis, patient report generation, additional cardiovascular conditions, and integration with hospital or healthcare systems.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Python Machine Learning Flask Scikit-learn Pandas NumPy HTML/CSS/JavaScript Random Forest Classifier</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1PXR42wTO0klucB-De4nUt4wwepenxNi6</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1EUibr2klxRYpHi10KporFv4d5GjDUgwg</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Muhammed Shammas CA</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>JEC23AD040</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>shammazrahiman36@gmail.com</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Muhammed Shiyas M</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>JEC23AD041</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Naseef Rahman Asharaf</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>JEC23AD043</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Mohamed UV</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>JEC23AD037</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>46250.89225375</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>avanthikaramesh.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Mini Project</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SECUREPIXELS:An AI Driven Chaotic Key Generation Framework For Secure Image Encryption In Sensitive Data Applications</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SECUREPIXELS: An AI Driven Chaotic Key Generation Framework for Secure Image Encryption in Sensitive Data Applications presents an adaptive, multi-layer image encryption framework designed to provide enhanced security for sensitive digital images. The proposed system combines chaotic-map-based key generation, machine learning-based map selection, confusion, diffusion, and inter-channel dependency to overcome the limitations of conventional fixed-key image encryption techniques.
+The encryption process begins with an input RGB image, which is separated into its Red, Green, and Blue channels. A machine learning model assists in selecting an appropriate chaotic map for the adaptive diffusion stage based on the characteristics of the input image and the encryption performance obtained from candidate maps. Image features such as entropy and standard deviation are evaluated to identify the chaotic system capable of producing a highly random encrypted output. Unlike the adaptive map, the Tent Map and Logistic Map are used as fixed chaotic components. The Tent Map generates a key sequence for bit-level permutation, rotation, and XOR operations, while the Logistic Map is used to modify inter-channel Hamming-distance matrices and strengthen channel dependency.
+The encryption framework consists of two major security principles: confusion and diffusion. In the confusion stages, global bit permutation and pixel-wise bit rotation disrupt the spatial and statistical relationships present in the original image. In the diffusion stages, Tent-map-based XOR operation is followed by adaptive chaotic feedback diffusion. The framework shown uses the Lorenz chaotic system as an example of the adaptively selected diffusion map, where its parameters and initial conditions generate a dynamic diffusion key. Feedback diffusion ensures that changes in one pixel can influence subsequent cipher pixels, thereby improving the avalanche effect. Furthermore, Hamming distances between the RGB channels are calculated and modified using the Logistic-map key, introducing additional inter-channel dependency. A final XOR masking operation combines the modified Hamming matrices with the diffused channels to produce the encrypted RGB cipher image.
+The proposed framework is intended for sensitive applications such as medical imaging, secure cloud storage, defense, and confidential image transmission. Its security can be evaluated using information entropy, histogram analysis, correlation coefficient, NPCR, UACI, key-space analysis, and key-sensitivity tests. By combining fixed chaotic mechanisms with AI-driven adaptive chaotic-map selection, SECUREPIXELS aims to provide stronger randomness, a large key space, improved resistance to statistical and differential attacks, and image-dependent encryption suitable for secure multimedia applications.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>MATLAB, Image Processing, Chaotic Maps, Machine Learning, Cryptography</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1eu_t7ehIXoS-1PKHwcRrL-MxKRvCVNhg</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1BceONfmfLlQYkqxWxrK8gdBANyZrgT3N</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Avanthika Ramesh</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>JEC23AD021</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>avanthikaramesh3002@gmail.com</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Jeevan Jaitas</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>JEC23AD032</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Mohamed Naizan PS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>JEC23AD036</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Sneya KM</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>JEC23AD054</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>46250.89452361111</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>muhammedshammasca.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Smart Fire Fighting System</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Fire accidents represent one of the most critical hazards in residential, industrial, and commercial environments, often leading to severe damage to property and posing a significant threat to human life. The rapid spread of fire and the delay in human response are the primary reasons for the escalation of such incidents. Therefore, the development of an automated system capable of detecting and suppressing fire at an early stage is of paramount importance. The Arduino Fire Fighting Robot with Auto Extinguisher is an embedded system designed to address this issue by providing an automated fire detection and extinguishing solution. The system employs a flame sensor capable of detecting infrared radiation emitted by fire sources. Once the presence of fire is detected, the signal is transmitted to the Arduino microcontroller, which acts as the central processing unit of the system. Based on this input, the Arduino activates servo motors that control the movement of a hose, allowing it to scan and align towards the direction of the fire. Simultaneously, a submersible water pump is triggered through a switching mechanism, enabling water to be sprayed directly onto the detected flame. The system continues its operation until the flame sensor no longer detects fire, ensuring complete extinguishment. This continuous monitoring and response mechanism enhances the reliability and effectiveness of the system. The proposed system demonstrates the application of embedded systems, automation, and control logic in real-world safety applications. It offers a low-cost, scalable, and efficient solution that can be implemented in small-scale environments such as workshops, laboratories, and homes. Furthermore, the system can be enhanced by integrating Internet of Things (IoT) technologies, mobile-based monitoring, and autonomous navigation features, making it suitable for large-scale industrial applications.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Arduino, Embedded Systems, C/C++, IoT, Sensors, Robotics, Automation, Servo Motor, Flame Sensor, Motor Control</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=14MxlXzRQ35WqQqVcXGd-HUGGAb8JukoL</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1Qg78WV3PaRiTv7vkx5GHzolC1Bm-9k5e</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Arjun K M</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Muhammed Shammas CA</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>JEC23AD040</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>shammazrahiman36@gmail.com</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Avanthika Ramesh</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>JEC23AD021</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Aquamol Tony</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>JEC23AD017</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Sneya KM</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>JEC23AD054</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>46250.90238168981</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>muhammedshammasca.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Mini Project</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>CAMPUS IN-MAPPING AND NAVIGATION</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>However, navigating the indoors within a large
+academic department is still a challenge because the availability
+of interactive digital guidance is limited. In this article, a smart
+indoor navigation system is presented for academic departmental
+environments using a 2D grid representation. The walkable
+and non-walkable zones are retrieved from the departmental
+layout and organized into a grid structure. An A* pathfinding
+algorithm with a Manhattan distance heuristic is employed for
+determining the optimal path between two classrooms. To make
+the system more user-friendly, a chatbot is also integrated into
+the smart indoor navigation system. The chatbot enables the
+user to specify the start and end points using a conversational
+dialogue. The smart indoor navigation system is developed using
+the ReactJS framework and is also planned for the integration
+of Augmented Reality (AR) technology for directional guidance.
+The experimental results show the accuracy of the path generated
+and the improvement in user interaction with the smart indoor
+navigation system.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>If you need exactly 4:  ReactJS, A *Algorithm, 2D Mapping, Chatbot</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1ZxNtR4Ox9m-XUrcRvbOp7-3BMu6dGpT4</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1gQJTTz89u5L26kqe1231Fyq0_TIsNAoL</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Leeshma O V</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Muhammed Shammas CA</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>JEC23AD040</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>shammazrahiman36@gmail.com</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Nandhana VP</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>JEC23AD042</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Amal PS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>LJEC23AD057</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Yasin Muhammed PM</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>LJEC23AD059</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>46250.92008983796</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>aquamoltony.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Main Project</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classification &amp; Identification Of Natyasasthra Stances Using Human Pose Estimation Algorithms </t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Natyasastra, authored by Sage Bharata, is one of the oldest and most authoritative treatises on
+Indian dramaturgy, dance, music, and theatre. It serves as the foundational text for all Indian
+classical dance forms. In Chapter 10 of the Natyasastra, nine fundamental body postures known as
+Sthanas are described. These Sthanas are classified into two categories: Purusha Sthanas
+(masculine postures)—Vaiṣṇavam, Samapādam, Vaiśākham, Maṇḍalam, Pratyālīḍham, and
+Ālīḍham—and Sthree Sthanas (feminine postures)—Āyatam, Avahittham, and Aśvakrāntam.
+These postures form the basis of correct body alignment and expression in Indian classical dance
+and are essential for performance, training, and preservation of traditional dance practices. Despite
+their significance, there is currently no automated system capable of recognizing these nine
+Sthanas, and the field lacks benchmark datasets and standardized computational approaches.
+Existing identification methods rely heavily on expert knowledge, making the process time
+consuming and subjective. This project proposes an automated Sthana recognition system using
+state-of-the-art human pose estimation techniques to identify the nine Sthanas described in the
+Natyasastra. A comprehensive image dataset covering all Purusha and Sthree Sthanas will be
+created, annotated, and validated by dance experts before being publicly released as a benchmark
+dataset.
+Human pose estimation is employed to extract skeletal keypoints representing body joints,
+enabling robust posture recognition while minimizing the influence of costume, lighting conditions, and background variations. The extracted pose features will be used to train deep
+learning-based classification models for accurate Sthana recognition. The proposed methodology
+includes dataset creation, expert annotation, pose estimation-based feature extraction, model
+training, and comparative evaluation of multiple pose estimation algorithms.
+The system will be evaluated using accuracy, precision, recall, F1-score, and inference time. The
+expected outcome is a publicly available benchmark dataset and a highly accurate automated
+Sthana classification system achieving classification accuracy above 95%, a macro F1-score of at
+least 0.95, and an inference time below 100 ms per image, thereby supporting real-time
+recognition, dance education, cultural heritage preservation, and future research at the intersection
+of Indian classical dance and computer vision</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CNN, Deep Learning, AI, Computer Vision, Human Pose Estimation </t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1OLOwP4wxy6k8ZpEQjGb8skm8oo7_Pb5X</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1kVIpBwa7AUJNrJsWthtrymWMoF6s0gLl</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Gayathri V</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aquamol Tony </t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>JEC23AD017</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>aquamoltony@gmail.com</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Bhuvanya VS</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>JEC23AD025</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Fathima Alzahra V A</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>JEC23AD027</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nived Krishna P </t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>JEC23AD044</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>46251.52831960648</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>hannahmargretms.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Sorting Numbers in Ascending and Descending Order</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Sorting Numbers in Ascending and Descending Order is a micro project based on Computer Organization and Architecture. The project implements the Bubble Sort algorithm using RISC-V assembly language to arrange a set of numbers in both ascending and descending order. The program uses registers, memory, comparison, branching, looping, and swapping instructions to perform the sorting process. The implementation is executed and analyzed using the RIPES (RISC-V Pipeline Simulator), which helps visualize register values, memory changes, instruction execution, and pipeline behavior. The project provides practical understanding of how high-level sorting logic is translated into low-level assembly instructions and how a processor executes these instructions. It also helps analyze concepts such as instruction count, clock cycles, CPI, and pipeline hazards. Overall, the project connects theoretical concepts of computer architecture with practical RISC-V assembly programming and processor-level execution.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>RISC-V, Assembly Language, Bubble Sort, RIPES Simulator, Computer Architecture, Processor Pipelining</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1eApF0zih6Bh87bVPCPL2UQJcpF6umIK0</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1PkoljU56b9AKKbO8QtU2McPUF8JE82M8</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sandeep C S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATHUL K K </t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>JEC24AD027</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>akkunni2005@gmail.com</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Faris Jaffer Sadik</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>JEC24AD040</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hannah Margret M S </t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>JEC24AD044</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isha fathima </t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>JEC24AD045</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>46251.57085719908</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>safwancsalam.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Second hand product prize estimator</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>The Second-Hand Product Price Estimator is a data-driven project in the domain of data science and machine learning, designed to evaluate and predict fair market prices for used items like vehicles, electronics, and household goods. In the rapidly expanding e-commerce landscape, second-hand marketplaces often lack standardized pricing mechanisms, making it difficult for buyers and sellers to determine fair value. Furthermore, consumers frequently face overpriced listings or fall victim to online fraudulent schemes. This project addresses these challenges by analyzing historical transaction data and specific product attributes to compute precise market estimations, thereby helping users verify whether a listed price is authentic or suspiciously inflated or underpriced.
+The primary objective of the system is to establish pricing transparency and mitigate online fraud. By processing essential variables such as brand reputation, item age, overall physical condition, original retail value, and current market demand, the predictive model calculates an objective, reasonable market range. Through this automated setup, users can input specific details of a pre-owned product and immediately evaluate listing credibility, shielding themselves from financial loss while empowering sellers to price their inventory competitively.
+From a technical perspective, the workflow begins with data collection from various e-commerce sources and classified listings. The raw dataset undergoes extensive cleaning and preprocessing to fix missing entries, encode categorical attributes like brand or item type, and scale numerical variables like usage duration. Exploratory Data Analysis (EDA) is then conducted to map statistical correlations between item characteristics and final selling prices. Using these insights, multiple regression algorithms—including Linear Regression, Decision Trees, and Random Forests—are trained and evaluated. Model accuracy is optimized and validated using standard evaluation metrics such as Mean Absolute Error (MAE) and Root Mean Squared Error (RMSE) to ensure minimal prediction variance.
+Ultimately, the Second-Hand Product Price Estimator acts as a reliable decision-support tool for peer-to-peer pre-owned trading platforms. By substituting subjective guessing with data-backed predictions, it builds consumer trust, reduces digital scams, and fosters sustainable economic habits by encouraging the reuse and recycling of pre-owned goods.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ai</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1CXivqZZFNGeTcYCAkyxb1gzr9jDmZTWb</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1jDlDpnAMpvc_Dl1EHGd4EMF6PUF6-X-_</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Safwan C Salam</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>JEC24AD074</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>safwancsalam1401@gmail.com</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Musthafa Nazar</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Jec24AD062</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Sana fathima pb</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Jec24AD076</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Sona CP</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>JEC24AD082</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>46251.57135085648</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>seannaks.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Early warning system to Cyclone detection using machine learning </t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Early Warning System for Cyclone Detection Using Machine Learning is a machine-learning project that predicts and classifies cyclone intensity using historical meteorological data from the IBTrACS dataset. The data is preprocessed using missing-value handling, feature engineering, encoding, and scaling, followed by a Random Forest classifier to predict cyclone intensity based on the Saffir–Simpson scale. The system aims to provide timely warnings, support evacuation and disaster preparedness, and reduce loss of life and property</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Project Area: Artificial Intelligence, Machine Learning, Data Science, Climate/Disaster Prediction Tech Stack: Python Machine Learning Random Forest Pandas NumPy Scikit-learn Data Preprocessing Data Visualization</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1aUYcgYZKeCLdn9dpaby8gXU34IXTwFUv</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1BR1lKC5eS___Tvxjuur8zV5mSWbyn9Gb</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seanna K S </t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>JEC24AD078</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>seannasubash@gmail.com</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Jones Maliyekkal Abraham</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>JEC24AD049</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Revathi G R</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>JEC24AD072</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stanes Wilson </t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>JEC24AD089</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>46251.57206666667</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>pranavpreman.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Used Book Price Prediction using Regression</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>The project preprocesses a used-book dataset by removing irrelevant features, extracting useful information, handling missing values, encoding categorical data, and normalizing numerical features so that regression algorithms can accurately predict used-book prices.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Python, Pandas, Scikit Learn, NumPy, Kaggle</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1lTVDvJIrSuZiapp3W5jYVSfA99JUfzgB</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=19Ok4N5gcraw4cRTU-VcE3fqElHHHhRRu</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Pranav Preman</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>JEC24AD071</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>pranavpreman133@gmail.com</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Oshly Jopko</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>JEC24AD066</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Midhu Sunil </t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>JEC24AD061</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Nashwa Shirin</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>JEC24AD063</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>46251.57241292824</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>sreedarshanvaliyaparambil.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RIVERSAFE - WATER BODY SAFETY MONITORING</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>The RiverSafe Project aims to ensure swimmer safety in rivers by predicting safe and
+unsafe river conditions using real-time data and machine learning. The system integrates
+rainfall and river flow velocity data to forecast flood risks and detect undercurrents that pose
+hazards to swimmers. This project uses the Kerala Floods Dataset (Kaggle) containing rainfall
+data from 1901 to 2017. The dataset underwent preprocessing steps such as handling missing
+values, scaling, and feature engineering, including the application of Manning’s Equation to
+estimate river flow velocity from rainfall data. To overcome the issue of limited data (only 118
+samples), data augmentation techniques were applied to synthetically expand the dataset to
+1,000 samples while maintaining realistic patterns and balanced class distribution. A Random
+Forest Classifier model was trained and evaluated using key performance metrics such as
+Recall and F1-score, achieving high reliability in predicting river safety. The project was
+implemented in Python using scikit-learn, pandas, and tkinter for GUI visualization. The visual
+interface allows users to input rainfall and velocity readings and receive immediate safety
+predictions. RiverSafe contributes to the Sustainable Development Goals (SDG 3:Good Health
+and Well Being, and SDG 13: Climate Action) by promoting safe recreational water use and
+leveraging technology for climate risk mitigation. The model demonstrates strong potential for
+integration with IoT sensors for real-time monitoring and can be extended to larger datasets to
+improve accuracy further.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1on5f7KZlGoIALK7t9Rhaj2tVfANhFB6e</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=189KR9wMcW9fMenndLYE5v5afdR7BUmTb</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SREEDARSHAN VALIYAPARAMBIL SANTHOSH KUMAR </t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC24AD083 </t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>sreedarshan70@gmail.com</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>VAISHNAVA O. J</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>JEC24AD090</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SHAN JOHNY</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>JEC24AD079</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>SREELAKSHMI M. P</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>JEC24AD085</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>46251.57443795139</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>staneswilson.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>E-COMMERCE INFORMATION SYSTEM: A  POLYGLOT PERSISTENCE APPROACH</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>The rapid expansion of digital retail necessitates database architectures capable of handling both strict transactional consistency and highly dynamic product attributes. Traditional monolithic RDBMS models often lead to sparse tables or complex EAV anti-patterns when managing diverse catalogs.
+This project implements an E-Commerce Information System built on a Polyglot Persistence strategy. PostgreSQL is used as the relational core to manage transactional entities (Users, Orders, Categories, Products Base) with full ACID compliance and referential integrity. Concurrently, MongoDB is integrated as a document store to handle flexible, schema-less product specifications and user reviews, logically bridged via the product SKU.
+At the database layer, PL/pgSQL triggers automate real-time inventory deductions upon order placement, while stored procedures with pessimistic row locking prevent race conditions and overselling during concurrent checkouts. The system is integrated into a modern web stack powered by Next.js 16, React 19, and Tailwind CSS v4, demonstrating a resilient and scalable backend architecture for modern digital commerce.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PostgreSQL, MongoDB, Next.js, React, Tailwind CSS, PL/pgSQL </t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1qV9FxFGi6TwicEJdKEVOD5FtwMkdfKBq</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1DMT4D-JfUNEmr3aELVGilm9eM_AjwxLG</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Stanes Wilson</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>JEC24AD089</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>staneswilson2006@gmail.com</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Shiyon Josy V</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>JEC24AD081</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Shaun Saji E</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>JEC24AD080</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Vaishnava O J</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>JEC24AD090</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46251.58087596065</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>sreedarshanvaliyaparambil.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Implementation of Bubble Sort Using RISC-V Assembly Language</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+High-level programming languages abstract away the internal workings of algorithms, making it difficult for learners to understand how operations are executed at the hardware level. This creates a gap in understanding between algorithm theory and actual execution.
+Therefore, there is a need to implement sorting algorithms like Bubble Sort using low-level instructions in RISC-V to clearly demonstrate how data is processed, compared, and stored in memory.
+ The main objective of this project is to implement Bubble Sort using RISC-V assembly language and understand how sorting is performed at the instruction level. It also aims to explore how registers and memory interact during execution.
+•Additionally, the project focuses on visualizing the sorting process using a simulator and analyzing how data changes step-by-step, improving the overall understanding of low-level programming concepts.</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>RISC-V</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1VqzbH8ZgUslUpzD0gKdJAUQnv5ytt0ZM</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=10uEkkKcg4i7s9hJZwpY83ze0g0IKW980</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Sajitha A S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SREEDARSHAN VALIYAPARAMBIL SANTHOSH KUMAR </t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC24AD083 </t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Sree-ctrl</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>SREELAKSHMI P</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>JEC24AD086</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SHAN JOHNY </t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>JEC24AD079</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>PAUL DIX</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>JEC24AD069</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46251.58119660879</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>samuelshajut.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ML-Based Nutrition Analysis</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ML-Based Nutrition Analysis is a machine learning project designed to classify common food items into three categories: Healthy, Moderate, and Unhealthy based on their nutritional content. The project uses a Kaggle dataset containing 1,000 records and nutritional features such as Calories, Fat, Sugar, Protein, Carbohydrates, Fibre, Sodium, and Price. Data preprocessing includes data validation, missing-value analysis, duplicate checking, outlier transformation, label encoding, and feature scaling. A Random Forest Classifier is used for the multi-class classification task because it can handle complex and non-linear relationships between nutritional features. The dataset is divided into training and testing sets, and the model is evaluated using accuracy, classification report, confusion matrix, and ROC/AUC analysis. The model achieved 96% accuracy, with Calories, Fat, and Fibre identified as important features. The final model is deployed as a functional web application using Gradio, allowing users to obtain food health classifications and make more informed, budget-friendly food choices. The project supports healthier eating and responsible consumption.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Python, Pandas, Scikit-learn, Random Forest, Machine Learning, Data Preprocessing, Gradio, Kaggle Dataset</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1zfeDW_0kSIzsbqQP67pzuFnMS1V9e_57</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=10bFPIX5lDAlE5JrsN6oUecCBp9RstxPt</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Samuel Shaju T</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JEC24AD075 </t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Samuel6ts@gmail.com</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Maria Ann Mathew</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>JEC24AD060</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Job John</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>JEC24AD047</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Keerthana krishna</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>JEC24AD054</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46251.58398221065</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>jovitjoshy.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Simple RISC-V Based Mini Banking System</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>The Simple RISC-V Based Mini Banking System is a basic banking application developed to demonstrate the practical application of RISC-V processor architecture and Computer Organization and Architecture (COA) concepts. The system is designed to perform common banking operations using RISC-V assembly instructions and a simple memory-based data structure.
+The proposed system provides basic features such as user authentication, balance enquiry, money deposit, money withdrawal, money transfer, and transaction management. The user interacts with the system through a simple menu-driven interface. The entered data is processed using RISC-V instructions, demonstrating arithmetic operations, logical operations, branching, memory access, registers, and subroutine calls.
+The project focuses on understanding how a high-level application can be implemented using low-level processor instructions. Account details such as account number, PIN, and balance are stored in memory, while RISC-V registers are used for temporary data processing. Conditional branch instructions are used to validate the PIN and check conditions such as sufficient balance during withdrawal and transfer operations.
+The system is intentionally kept simple so that the relationship between the banking operations and the underlying RISC-V architecture can be clearly understood. It demonstrates important COA concepts including instruction execution, register utilization, memory organization, arithmetic and logical operations, control flow, and input/output handling.
+The project can be implemented and tested using a RISC-V simulator or emulator, making it suitable for educational purposes. Overall, the project provides a practical understanding of RISC-V architecture by combining processor-level programming with a real-world banking application.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>RISC-V Assembly, RISC-V ISA, RARS Simulator, Computer Organization &amp; Architecture, Memory Management, Assembly Programming</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1LLTZII5JIj-FDn2YT5_zV4R914K12qOA</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1LLyF1JveLpHr9nBRifL78xkEWSsHAeR9</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sajitha A S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Jovit Joshy</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>JEC24AD052</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>KookieMonster97</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Keerthana Krishna</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>JEC24AD054</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Sreelakshmi Ajithan</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>JEC24AD084</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Seanna K. S</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>JEC24AD078</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>46251.59147627315</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>sreedarshanvaliyaparambil.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Design and Implementation of an AI-Powered Intelligent Trip Planning and Railway Management Database System</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Modern railway and transit networks suffer from
+fragmented routing paradigms, requiring passengers to
+manually synthesize multi-train itineraries or calculate
+alternative connection vectors during periods of peak seasonal
+traffic or systemic delays. This comprehensive study introduces
+an AI-powered, web-based Railway Management Database
+System integrated with a robust, client-aware Intelligent Trip
+Planning optimization framework. Moving beyond legacy
+transactional structures that merely record static data, our
+architecture deploys a specialized heuristic graph-search
+routing layer capable of computing globally optimal multi-
+destination itineraries based on real-time schedule variations,
+multi-modal transfer properties, and individualized passenger
+preference weights. The multi-tiered application leverages
+HTML5/CSS3/JS for the responsive presentation interface, a
+lightweight Python-based Flask micro-framework for backend
+asynchronous route handling, and a highly structured MySQL
+relational database engine for operational persistence. Strict
+ACID compliance and data consistency are actively preserved
+via native database-level constraints and atomic triggers
+designed to eliminate race conditions and seat over-allocation
+during peak booking checkouts. Experimental simulations
+generated over thousands of concurrent nodes demonstrate the
+system's ability to execute sub-20ms pathfinder queries across
+complex, dense route networks while maintaining absolute
+transactional integrity under heavy concurrent write loads. The
+results highlight a paradigm shift in transit management,
+marrying advanced predictive artificial intelligence with
+deterministic relational database security.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>AI, ML</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1HJXkHkYImyFUvuaCp_8Qz1w3hNYLNZwk</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1Er6HcNgZ5bsDB1cVGl5b-vgIqExl1js6</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SREEDARSHAN VALIYAPARAMBIL SANTHOSH KUMAR </t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>JEC24AD083</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Sree-Ctrl</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>JOSEPH GEO PANAKKAL</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>JEC24AD050</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SHAN JOHNY</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>JEC24AD079</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>JOSEPH K BABU</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>JEC24AD051</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>46251.61139574074</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>rosmilakt.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Mini Project</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AI-BASED MULTIMODAL INVASIVE PLANT  SPECIES IDENTIFICATION USING OPTICAL,  THERMAL, AND VOC SENSOR DATA</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Invasive plant species pose a significant threat to the biodiversity, agriculture and ecosystem 
+stability. Identifying these species at early stage is crucial for effective ecosystem 
+management and conservation efforts. However traditional monitoring method mainly 
+depends on manual field survey or single data sources such as optical images, which are often 
+time consuming, costly, and less reliable, especially during the early stages of invasion.To 
+address these challenges, this work proposes an AI-based multimodal framework that 
+integrate optical imagery, thermal signatures, and Volatile Organic Compound (VOC) sensor 
+data for robust invasive species identification. Optical imagery is utilized to capture visual 
+characteristics such as colour, texture, and morphological features of plant species, while 
+thermal data provides complementary information related to plant stress and physiological 
+behaviour. Additionally, VOC sensor data is incorporated to analyse species-specific 
+chemical emissions, enabling improved discrimination between visually similar invasive and 
+native plants. Deep learning techniques are used to extract meaningful features from each 
+data source, and a data fusion approach is applied to classify plants as invasive or native. A 
+multimodal feature fusion strategy is then applied to combine the extracted features and 
+perform accurate classification of plant species as invasive or native.The proposed 
+framework offers an effective and intelligent solution for automated invasive species 
+detection and can support sustainable ecosystem management and biodiversity conservation 
+efforts.</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI, CNN, Deep Learning, Thermal Imaging </t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=11FI1KBHQd85mugDVhRPN9yuoUw2CtF_K</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=11UUkuQRvRUgwvrPtj_8PIbyT7LIxxcUI</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Nikhitha N</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rosmila K T </t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>JEC23AD049</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://github.com/Rosmilakt</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Aron Tom Bosco Melit</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>JEC23AD019</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Ayush V S</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>JEC23AD024</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Jabzin Jaisul</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>JEC23AD031</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>46251.66748511574</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>keerthyk.ad23@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2023-27 (S7)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fit Finder </t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>FitFinder is an intelligent fashion assistance system designed to help users select suitable clothing sizes and colors based on their personal body measurements and skin tone. Choosing the correct clothing size and suitable colors can be challenging, especially when shopping online, where users cannot physically try on garments. FitFinder addresses these issues by providing personalized size prediction and color recommendations through a simple and user-friendly web application.
+The system provides two major functionalities: clothing size prediction and personalized color analysis. For size prediction, users enter relevant information such as gender, height, weight, chest measurement, waist measurement, body-fit preference, and inseam length. These inputs are processed by a machine learning-based prediction model to recommend an appropriate clothing size along with additional fit information. This helps users make more confident clothing choices and can potentially reduce incorrect-size purchases.
+The color analysis feature allows users to upload a photograph for analysis. The system processes the uploaded image to identify the user's skin tone and extracts relevant color information using image-processing techniques. Based on the analyzed tone, the application recommends a suitable range of clothing colors that can complement the user's appearance. The system displays multiple suggested colors, making it easier for users to select appropriate outfits.
+The application combines machine learning, image processing, and web technologies to provide an integrated personalized fashion recommendation platform. Its workflow involves collecting user information, processing the provided measurements or uploaded image, applying the respective prediction or analysis technique, and presenting the results in an easy-to-understand format. The system is designed with a simple interface so that users can obtain recommendations quickly without requiring specialized knowledge.
+FitFinder can be particularly useful for online shoppers, fashion enthusiasts, e-commerce platforms, and clothing retailers. By combining size prediction with personalized color recommendations, the system aims to improve the online shopping experience, support better fashion decisions, and increase user confidence when selecting clothing.</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Machine Learning, Computer Vision, and Fashion Technology</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1fF4KylpZ89SdgLf5TjNCrrHroo-nefy3</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1lmvggHKkziE2ZRalgx3eyzoRY-_PYqhe</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Jithin K C</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Keerthy K</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>JEC23AD033</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://github.com/KeerthyKrishnadas</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aquamol Tony </t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>JEC23AD017</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aishwarya Dinesh Rao </t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>JEC23AD005</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Hiba Rebin K</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>JEC23AD029</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>46251.84908905093</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>akhilbijuthudumel.ad24@jecc.ac.in</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2024-28 (S5)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Micro Project</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Pipeline Hazard Analysis in Risk-V Processor</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>The main objective of this project is to study and analyze pipeline hazards in RISC-V processors and understand their impact on system performance. The project aims to provide both theoretical knowledge and practical insights into how pipelining works and how hazards can be effectively managed.</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Ripes, Risk-V, python, VScode</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1Yo9y4Gfp2GZMsWQoIQrZ_lK4jMKZ9DXg</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=1M3Km0Y5wywMm6oCTCCoJ1OZX3c1IPxlC</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Sandeep C S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>AKHIL BIJU THUDUMEL</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>JEC24AD009</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>akhil80610</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>AADITI SANDEEP</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>JEC24AD001</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>ABHIJITH NAMBIAR</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>JEC24AD002</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>ASWATHY S</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>JEC24AD026</t>
         </is>
       </c>
     </row>
